--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,33 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
+    <t>['7', '33']</t>
+  </si>
+  <si>
+    <t>[]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +806,212 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7796868</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45752.67708333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2">
+        <v>1.57</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+      <c r="S2">
+        <v>7</v>
+      </c>
+      <c r="T2">
+        <v>1.2</v>
+      </c>
+      <c r="U2">
+        <v>4.33</v>
+      </c>
+      <c r="V2">
+        <v>1.83</v>
+      </c>
+      <c r="W2">
+        <v>1.83</v>
+      </c>
+      <c r="X2">
+        <v>3.75</v>
+      </c>
+      <c r="Y2">
+        <v>1.25</v>
+      </c>
+      <c r="Z2">
+        <v>1.23</v>
+      </c>
+      <c r="AA2">
+        <v>7</v>
+      </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
+      <c r="AC2">
+        <v>1.01</v>
+      </c>
+      <c r="AD2">
+        <v>21</v>
+      </c>
+      <c r="AE2">
+        <v>1.04</v>
+      </c>
+      <c r="AF2">
+        <v>7.1</v>
+      </c>
+      <c r="AG2">
+        <v>1.3</v>
+      </c>
+      <c r="AH2">
+        <v>3.4</v>
+      </c>
+      <c r="AI2">
+        <v>1.67</v>
+      </c>
+      <c r="AJ2">
+        <v>2.1</v>
+      </c>
+      <c r="AK2">
+        <v>1.03</v>
+      </c>
+      <c r="AL2">
+        <v>1.09</v>
+      </c>
+      <c r="AM2">
+        <v>4.1</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>10</v>
+      </c>
+      <c r="AV2">
+        <v>3</v>
+      </c>
+      <c r="AW2">
+        <v>14</v>
+      </c>
+      <c r="AX2">
+        <v>2</v>
+      </c>
+      <c r="AY2">
+        <v>24</v>
+      </c>
+      <c r="AZ2">
+        <v>5</v>
+      </c>
+      <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>4</v>
+      </c>
+      <c r="BC2">
+        <v>11</v>
+      </c>
+      <c r="BD2">
+        <v>1.14</v>
+      </c>
+      <c r="BE2">
+        <v>13</v>
+      </c>
+      <c r="BF2">
+        <v>6.5</v>
+      </c>
+      <c r="BG2">
+        <v>1.08</v>
+      </c>
+      <c r="BH2">
+        <v>6.05</v>
+      </c>
+      <c r="BI2">
+        <v>1.18</v>
+      </c>
+      <c r="BJ2">
+        <v>3.84</v>
+      </c>
+      <c r="BK2">
+        <v>1.36</v>
+      </c>
+      <c r="BL2">
+        <v>2.7</v>
+      </c>
+      <c r="BM2">
+        <v>1.63</v>
+      </c>
+      <c r="BN2">
+        <v>2.09</v>
+      </c>
+      <c r="BO2">
+        <v>2.04</v>
+      </c>
+      <c r="BP2">
+        <v>1.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="85">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -229,13 +229,46 @@
     <t>Breidablik</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Vestri</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>ÍA</t>
+  </si>
+  <si>
     <t>['7', '33']</t>
   </si>
   <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['25', '32']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['11', '44']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -597,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP2"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -829,7 +862,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -850,10 +883,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="Q2">
         <v>1.57</v>
@@ -1010,6 +1043,624 @@
       </c>
       <c r="BP2">
         <v>1.69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7796869</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45753.45833333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3">
+        <v>1.73</v>
+      </c>
+      <c r="R3">
+        <v>2.75</v>
+      </c>
+      <c r="S3">
+        <v>5.5</v>
+      </c>
+      <c r="T3">
+        <v>1.2</v>
+      </c>
+      <c r="U3">
+        <v>4.33</v>
+      </c>
+      <c r="V3">
+        <v>1.83</v>
+      </c>
+      <c r="W3">
+        <v>1.83</v>
+      </c>
+      <c r="X3">
+        <v>3.75</v>
+      </c>
+      <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>1.3</v>
+      </c>
+      <c r="AA3">
+        <v>5.6</v>
+      </c>
+      <c r="AB3">
+        <v>6.5</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>1.04</v>
+      </c>
+      <c r="AF3">
+        <v>6.9</v>
+      </c>
+      <c r="AG3">
+        <v>1.3</v>
+      </c>
+      <c r="AH3">
+        <v>3.21</v>
+      </c>
+      <c r="AI3">
+        <v>1.53</v>
+      </c>
+      <c r="AJ3">
+        <v>2.38</v>
+      </c>
+      <c r="AK3">
+        <v>1.1</v>
+      </c>
+      <c r="AL3">
+        <v>1.14</v>
+      </c>
+      <c r="AM3">
+        <v>3.1</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>4</v>
+      </c>
+      <c r="AW3">
+        <v>5</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>12</v>
+      </c>
+      <c r="AZ3">
+        <v>4</v>
+      </c>
+      <c r="BA3">
+        <v>7</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>7</v>
+      </c>
+      <c r="BD3">
+        <v>1.31</v>
+      </c>
+      <c r="BE3">
+        <v>10</v>
+      </c>
+      <c r="BF3">
+        <v>4.11</v>
+      </c>
+      <c r="BG3">
+        <v>1.08</v>
+      </c>
+      <c r="BH3">
+        <v>5.85</v>
+      </c>
+      <c r="BI3">
+        <v>1.18</v>
+      </c>
+      <c r="BJ3">
+        <v>4.05</v>
+      </c>
+      <c r="BK3">
+        <v>1.34</v>
+      </c>
+      <c r="BL3">
+        <v>2.97</v>
+      </c>
+      <c r="BM3">
+        <v>1.59</v>
+      </c>
+      <c r="BN3">
+        <v>2.27</v>
+      </c>
+      <c r="BO3">
+        <v>1.91</v>
+      </c>
+      <c r="BP3">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7796870</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45753.55208333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q4">
+        <v>3.12</v>
+      </c>
+      <c r="R4">
+        <v>2.59</v>
+      </c>
+      <c r="S4">
+        <v>2.51</v>
+      </c>
+      <c r="T4">
+        <v>1.13</v>
+      </c>
+      <c r="U4">
+        <v>4.75</v>
+      </c>
+      <c r="V4">
+        <v>1.87</v>
+      </c>
+      <c r="W4">
+        <v>1.87</v>
+      </c>
+      <c r="X4">
+        <v>3.75</v>
+      </c>
+      <c r="Y4">
+        <v>1.21</v>
+      </c>
+      <c r="Z4">
+        <v>2.5</v>
+      </c>
+      <c r="AA4">
+        <v>4</v>
+      </c>
+      <c r="AB4">
+        <v>2.25</v>
+      </c>
+      <c r="AC4">
+        <v>1.01</v>
+      </c>
+      <c r="AD4">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>1.02</v>
+      </c>
+      <c r="AF4">
+        <v>8</v>
+      </c>
+      <c r="AG4">
+        <v>1.29</v>
+      </c>
+      <c r="AH4">
+        <v>3.27</v>
+      </c>
+      <c r="AI4">
+        <v>1.28</v>
+      </c>
+      <c r="AJ4">
+        <v>3.34</v>
+      </c>
+      <c r="AK4">
+        <v>1.7</v>
+      </c>
+      <c r="AL4">
+        <v>1.22</v>
+      </c>
+      <c r="AM4">
+        <v>1.41</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>5</v>
+      </c>
+      <c r="AW4">
+        <v>6</v>
+      </c>
+      <c r="AX4">
+        <v>7</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>12</v>
+      </c>
+      <c r="BA4">
+        <v>9</v>
+      </c>
+      <c r="BB4">
+        <v>2</v>
+      </c>
+      <c r="BC4">
+        <v>11</v>
+      </c>
+      <c r="BD4">
+        <v>2.1</v>
+      </c>
+      <c r="BE4">
+        <v>9</v>
+      </c>
+      <c r="BF4">
+        <v>1.91</v>
+      </c>
+      <c r="BG4">
+        <v>1.08</v>
+      </c>
+      <c r="BH4">
+        <v>6.1</v>
+      </c>
+      <c r="BI4">
+        <v>1.15</v>
+      </c>
+      <c r="BJ4">
+        <v>4.4</v>
+      </c>
+      <c r="BK4">
+        <v>1.29</v>
+      </c>
+      <c r="BL4">
+        <v>3.15</v>
+      </c>
+      <c r="BM4">
+        <v>1.51</v>
+      </c>
+      <c r="BN4">
+        <v>2.39</v>
+      </c>
+      <c r="BO4">
+        <v>1.8</v>
+      </c>
+      <c r="BP4">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7796871</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45753.67708333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5">
+        <v>2.83</v>
+      </c>
+      <c r="R5">
+        <v>2.32</v>
+      </c>
+      <c r="S5">
+        <v>3.12</v>
+      </c>
+      <c r="T5">
+        <v>1.24</v>
+      </c>
+      <c r="U5">
+        <v>3.5</v>
+      </c>
+      <c r="V5">
+        <v>2.18</v>
+      </c>
+      <c r="W5">
+        <v>1.64</v>
+      </c>
+      <c r="X5">
+        <v>4.6</v>
+      </c>
+      <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>2.3</v>
+      </c>
+      <c r="AA5">
+        <v>3.5</v>
+      </c>
+      <c r="AB5">
+        <v>2.75</v>
+      </c>
+      <c r="AC5">
+        <v>1.01</v>
+      </c>
+      <c r="AD5">
+        <v>13</v>
+      </c>
+      <c r="AE5">
+        <v>1.11</v>
+      </c>
+      <c r="AF5">
+        <v>4.95</v>
+      </c>
+      <c r="AG5">
+        <v>1.46</v>
+      </c>
+      <c r="AH5">
+        <v>2.52</v>
+      </c>
+      <c r="AI5">
+        <v>1.41</v>
+      </c>
+      <c r="AJ5">
+        <v>2.69</v>
+      </c>
+      <c r="AK5">
+        <v>1.46</v>
+      </c>
+      <c r="AL5">
+        <v>1.27</v>
+      </c>
+      <c r="AM5">
+        <v>1.54</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>2</v>
+      </c>
+      <c r="AV5">
+        <v>4</v>
+      </c>
+      <c r="AW5">
+        <v>7</v>
+      </c>
+      <c r="AX5">
+        <v>8</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>12</v>
+      </c>
+      <c r="BA5">
+        <v>10</v>
+      </c>
+      <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BC5">
+        <v>13</v>
+      </c>
+      <c r="BD5">
+        <v>1.95</v>
+      </c>
+      <c r="BE5">
+        <v>8.5</v>
+      </c>
+      <c r="BF5">
+        <v>2.05</v>
+      </c>
+      <c r="BG5">
+        <v>1.08</v>
+      </c>
+      <c r="BH5">
+        <v>5.85</v>
+      </c>
+      <c r="BI5">
+        <v>1.18</v>
+      </c>
+      <c r="BJ5">
+        <v>4.05</v>
+      </c>
+      <c r="BK5">
+        <v>1.34</v>
+      </c>
+      <c r="BL5">
+        <v>2.97</v>
+      </c>
+      <c r="BM5">
+        <v>1.59</v>
+      </c>
+      <c r="BN5">
+        <v>2.27</v>
+      </c>
+      <c r="BO5">
+        <v>1.92</v>
+      </c>
+      <c r="BP5">
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,12 @@
     <t>Fram</t>
   </si>
   <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
@@ -250,6 +256,12 @@
     <t>ÍA</t>
   </si>
   <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
     <t>['7', '33']</t>
   </si>
   <si>
@@ -262,6 +274,12 @@
     <t>[]</t>
   </si>
   <si>
+    <t>['49', '79']</t>
+  </si>
+  <si>
+    <t>['64', '68']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -269,6 +287,9 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['90']</t>
   </si>
 </sst>
 </file>
@@ -630,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -862,7 +883,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -883,10 +904,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q2">
         <v>1.57</v>
@@ -1068,7 +1089,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1089,10 +1110,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1274,7 +1295,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1295,10 +1316,10 @@
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1480,7 +1501,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1501,10 +1522,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -1661,6 +1682,418 @@
       </c>
       <c r="BP5">
         <v>1.82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7796872</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45754.625</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q6">
+        <v>1.67</v>
+      </c>
+      <c r="R6">
+        <v>2.88</v>
+      </c>
+      <c r="S6">
+        <v>6.5</v>
+      </c>
+      <c r="T6">
+        <v>1.2</v>
+      </c>
+      <c r="U6">
+        <v>4.33</v>
+      </c>
+      <c r="V6">
+        <v>1.91</v>
+      </c>
+      <c r="W6">
+        <v>1.8</v>
+      </c>
+      <c r="X6">
+        <v>4</v>
+      </c>
+      <c r="Y6">
+        <v>1.22</v>
+      </c>
+      <c r="Z6">
+        <v>1.3</v>
+      </c>
+      <c r="AA6">
+        <v>5.9</v>
+      </c>
+      <c r="AB6">
+        <v>7.5</v>
+      </c>
+      <c r="AC6">
+        <v>1.01</v>
+      </c>
+      <c r="AD6">
+        <v>26</v>
+      </c>
+      <c r="AE6">
+        <v>1.06</v>
+      </c>
+      <c r="AF6">
+        <v>6.35</v>
+      </c>
+      <c r="AG6">
+        <v>1.3</v>
+      </c>
+      <c r="AH6">
+        <v>3.21</v>
+      </c>
+      <c r="AI6">
+        <v>1.62</v>
+      </c>
+      <c r="AJ6">
+        <v>2.2</v>
+      </c>
+      <c r="AK6">
+        <v>1.06</v>
+      </c>
+      <c r="AL6">
+        <v>1.12</v>
+      </c>
+      <c r="AM6">
+        <v>3.5</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>6</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>5</v>
+      </c>
+      <c r="AX6">
+        <v>4</v>
+      </c>
+      <c r="AY6">
+        <v>11</v>
+      </c>
+      <c r="AZ6">
+        <v>4</v>
+      </c>
+      <c r="BA6">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>7</v>
+      </c>
+      <c r="BD6">
+        <v>1.3</v>
+      </c>
+      <c r="BE6">
+        <v>11</v>
+      </c>
+      <c r="BF6">
+        <v>4.38</v>
+      </c>
+      <c r="BG6">
+        <v>1.08</v>
+      </c>
+      <c r="BH6">
+        <v>6.15</v>
+      </c>
+      <c r="BI6">
+        <v>1.17</v>
+      </c>
+      <c r="BJ6">
+        <v>4.2</v>
+      </c>
+      <c r="BK6">
+        <v>1.31</v>
+      </c>
+      <c r="BL6">
+        <v>3.05</v>
+      </c>
+      <c r="BM6">
+        <v>1.54</v>
+      </c>
+      <c r="BN6">
+        <v>2.31</v>
+      </c>
+      <c r="BO6">
+        <v>1.87</v>
+      </c>
+      <c r="BP6">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7796873</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45754.67708333334</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7">
+        <v>2.6</v>
+      </c>
+      <c r="R7">
+        <v>2.4</v>
+      </c>
+      <c r="S7">
+        <v>3.2</v>
+      </c>
+      <c r="T7">
+        <v>1.25</v>
+      </c>
+      <c r="U7">
+        <v>3.75</v>
+      </c>
+      <c r="V7">
+        <v>2.1</v>
+      </c>
+      <c r="W7">
+        <v>1.67</v>
+      </c>
+      <c r="X7">
+        <v>4.5</v>
+      </c>
+      <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>2.19</v>
+      </c>
+      <c r="AA7">
+        <v>4</v>
+      </c>
+      <c r="AB7">
+        <v>2.74</v>
+      </c>
+      <c r="AC7">
+        <v>1.01</v>
+      </c>
+      <c r="AD7">
+        <v>17</v>
+      </c>
+      <c r="AE7">
+        <v>1.09</v>
+      </c>
+      <c r="AF7">
+        <v>5.3</v>
+      </c>
+      <c r="AG7">
+        <v>1.42</v>
+      </c>
+      <c r="AH7">
+        <v>2.65</v>
+      </c>
+      <c r="AI7">
+        <v>1.44</v>
+      </c>
+      <c r="AJ7">
+        <v>2.63</v>
+      </c>
+      <c r="AK7">
+        <v>1.36</v>
+      </c>
+      <c r="AL7">
+        <v>1.27</v>
+      </c>
+      <c r="AM7">
+        <v>1.68</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>4</v>
+      </c>
+      <c r="AV7">
+        <v>3</v>
+      </c>
+      <c r="AW7">
+        <v>3</v>
+      </c>
+      <c r="AX7">
+        <v>8</v>
+      </c>
+      <c r="AY7">
+        <v>7</v>
+      </c>
+      <c r="AZ7">
+        <v>11</v>
+      </c>
+      <c r="BA7">
+        <v>6</v>
+      </c>
+      <c r="BB7">
+        <v>8</v>
+      </c>
+      <c r="BC7">
+        <v>14</v>
+      </c>
+      <c r="BD7">
+        <v>2.1</v>
+      </c>
+      <c r="BE7">
+        <v>9</v>
+      </c>
+      <c r="BF7">
+        <v>1.91</v>
+      </c>
+      <c r="BG7">
+        <v>1.08</v>
+      </c>
+      <c r="BH7">
+        <v>6.15</v>
+      </c>
+      <c r="BI7">
+        <v>1.17</v>
+      </c>
+      <c r="BJ7">
+        <v>4.2</v>
+      </c>
+      <c r="BK7">
+        <v>1.31</v>
+      </c>
+      <c r="BL7">
+        <v>3.05</v>
+      </c>
+      <c r="BM7">
+        <v>1.54</v>
+      </c>
+      <c r="BN7">
+        <v>2.31</v>
+      </c>
+      <c r="BO7">
+        <v>1.87</v>
+      </c>
+      <c r="BP7">
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="171">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -412,6 +412,9 @@
     <t>['50', '68']</t>
   </si>
   <si>
+    <t>['18', '63', '68']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -521,6 +524,9 @@
   </si>
   <si>
     <t>['64']</t>
+  </si>
+  <si>
+    <t>['27', '78']</t>
   </si>
 </sst>
 </file>
@@ -882,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP61"/>
+  <dimension ref="A1:BP62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1344,7 +1350,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1550,7 +1556,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1756,7 +1762,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2168,7 +2174,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2246,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2992,7 +2998,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3276,7 +3282,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3404,7 +3410,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3485,7 +3491,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3610,7 +3616,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3816,7 +3822,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4022,7 +4028,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4228,7 +4234,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4434,7 +4440,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4846,7 +4852,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5052,7 +5058,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5464,7 +5470,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5542,7 +5548,7 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ23">
         <v>1.17</v>
@@ -5876,7 +5882,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6082,7 +6088,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6575,7 +6581,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -6906,7 +6912,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7112,7 +7118,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7524,7 +7530,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7730,7 +7736,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8014,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ35">
         <v>0.6</v>
@@ -8142,7 +8148,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8348,7 +8354,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q37">
         <v>1.91</v>
@@ -8966,7 +8972,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9172,7 +9178,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9250,7 +9256,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9378,7 +9384,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9459,7 +9465,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>2.48</v>
@@ -9584,7 +9590,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9790,7 +9796,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10408,7 +10414,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10614,7 +10620,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11026,7 +11032,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11232,7 +11238,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11313,7 +11319,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.5</v>
@@ -11438,7 +11444,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11644,7 +11650,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11850,7 +11856,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12056,7 +12062,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12134,7 +12140,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ55">
         <v>0.6</v>
@@ -12468,7 +12474,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q57">
         <v>2.8</v>
@@ -12880,7 +12886,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13292,7 +13298,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13449,6 +13455,212 @@
       </c>
       <c r="BP61">
         <v>1.84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:68">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>7796933</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45822.67708333334</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>2</v>
+      </c>
+      <c r="L62">
+        <v>3</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62">
+        <v>5</v>
+      </c>
+      <c r="O62" t="s">
+        <v>132</v>
+      </c>
+      <c r="P62" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q62">
+        <v>3.55</v>
+      </c>
+      <c r="R62">
+        <v>2.48</v>
+      </c>
+      <c r="S62">
+        <v>2.1</v>
+      </c>
+      <c r="T62">
+        <v>1.17</v>
+      </c>
+      <c r="U62">
+        <v>4.3</v>
+      </c>
+      <c r="V62">
+        <v>1.9</v>
+      </c>
+      <c r="W62">
+        <v>1.81</v>
+      </c>
+      <c r="X62">
+        <v>3.8</v>
+      </c>
+      <c r="Y62">
+        <v>1.22</v>
+      </c>
+      <c r="Z62">
+        <v>3.15</v>
+      </c>
+      <c r="AA62">
+        <v>4</v>
+      </c>
+      <c r="AB62">
+        <v>1.86</v>
+      </c>
+      <c r="AC62">
+        <v>1.01</v>
+      </c>
+      <c r="AD62">
+        <v>18</v>
+      </c>
+      <c r="AE62">
+        <v>1.06</v>
+      </c>
+      <c r="AF62">
+        <v>7</v>
+      </c>
+      <c r="AG62">
+        <v>1.33</v>
+      </c>
+      <c r="AH62">
+        <v>3</v>
+      </c>
+      <c r="AI62">
+        <v>1.33</v>
+      </c>
+      <c r="AJ62">
+        <v>2.9</v>
+      </c>
+      <c r="AK62">
+        <v>1.22</v>
+      </c>
+      <c r="AL62">
+        <v>1.2</v>
+      </c>
+      <c r="AM62">
+        <v>1.25</v>
+      </c>
+      <c r="AN62">
+        <v>2.17</v>
+      </c>
+      <c r="AO62">
+        <v>1</v>
+      </c>
+      <c r="AP62">
+        <v>2.29</v>
+      </c>
+      <c r="AQ62">
+        <v>0.8</v>
+      </c>
+      <c r="AR62">
+        <v>1.53</v>
+      </c>
+      <c r="AS62">
+        <v>1.47</v>
+      </c>
+      <c r="AT62">
+        <v>3</v>
+      </c>
+      <c r="AU62">
+        <v>11</v>
+      </c>
+      <c r="AV62">
+        <v>5</v>
+      </c>
+      <c r="AW62">
+        <v>7</v>
+      </c>
+      <c r="AX62">
+        <v>6</v>
+      </c>
+      <c r="AY62">
+        <v>18</v>
+      </c>
+      <c r="AZ62">
+        <v>11</v>
+      </c>
+      <c r="BA62">
+        <v>13</v>
+      </c>
+      <c r="BB62">
+        <v>3</v>
+      </c>
+      <c r="BC62">
+        <v>16</v>
+      </c>
+      <c r="BD62">
+        <v>2.81</v>
+      </c>
+      <c r="BE62">
+        <v>7.7</v>
+      </c>
+      <c r="BF62">
+        <v>1.54</v>
+      </c>
+      <c r="BG62">
+        <v>1.1</v>
+      </c>
+      <c r="BH62">
+        <v>5.75</v>
+      </c>
+      <c r="BI62">
+        <v>1.15</v>
+      </c>
+      <c r="BJ62">
+        <v>4.75</v>
+      </c>
+      <c r="BK62">
+        <v>1.29</v>
+      </c>
+      <c r="BL62">
+        <v>3.35</v>
+      </c>
+      <c r="BM62">
+        <v>1.48</v>
+      </c>
+      <c r="BN62">
+        <v>2.5</v>
+      </c>
+      <c r="BO62">
+        <v>1.72</v>
+      </c>
+      <c r="BP62">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="175">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -415,6 +415,15 @@
     <t>['18', '63', '68']</t>
   </si>
   <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['76', '6']</t>
+  </si>
+  <si>
+    <t>['71', '85', '90+1', '33']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -478,9 +487,6 @@
     <t>['13']</t>
   </si>
   <si>
-    <t>['35']</t>
-  </si>
-  <si>
     <t>['6', '9', '58']</t>
   </si>
   <si>
@@ -526,7 +532,13 @@
     <t>['64']</t>
   </si>
   <si>
-    <t>['27', '78']</t>
+    <t>['26', '77']</t>
+  </si>
+  <si>
+    <t>['20', '76']</t>
+  </si>
+  <si>
+    <t>['17']</t>
   </si>
 </sst>
 </file>
@@ -888,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP62"/>
+  <dimension ref="A1:BP66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1350,7 +1362,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1556,7 +1568,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1762,7 +1774,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -1840,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2174,7 +2186,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -2255,7 +2267,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2458,10 +2470,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2664,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ9">
         <v>1.17</v>
@@ -2873,7 +2885,7 @@
         <v>3</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>1.61</v>
@@ -2998,7 +3010,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3076,10 +3088,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
+        <v>2</v>
+      </c>
+      <c r="AQ11">
         <v>1.8</v>
-      </c>
-      <c r="AQ11">
-        <v>1.5</v>
       </c>
       <c r="AR11">
         <v>1.39</v>
@@ -3285,7 +3297,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR12">
         <v>1.35</v>
@@ -3410,7 +3422,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3616,7 +3628,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3697,7 +3709,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ14">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR14">
         <v>2.07</v>
@@ -3822,7 +3834,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4028,7 +4040,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4234,7 +4246,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4440,7 +4452,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4518,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18">
         <v>0.6</v>
@@ -4724,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -4852,7 +4864,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -4930,10 +4942,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
+        <v>2</v>
+      </c>
+      <c r="AQ20">
         <v>1.8</v>
-      </c>
-      <c r="AQ20">
-        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>0.64</v>
@@ -5058,7 +5070,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5139,7 +5151,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR21">
         <v>1.55</v>
@@ -5345,7 +5357,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5470,7 +5482,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5754,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>0.2</v>
@@ -5882,7 +5894,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6088,7 +6100,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6166,7 +6178,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>1.4</v>
@@ -6375,7 +6387,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ27">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR27">
         <v>1.96</v>
@@ -6784,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ29">
         <v>0.25</v>
@@ -6912,7 +6924,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7118,7 +7130,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7402,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>0.2</v>
@@ -7530,7 +7542,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7736,7 +7748,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -7817,7 +7829,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR34">
         <v>1.97</v>
@@ -8148,7 +8160,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8229,7 +8241,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ36">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR36">
         <v>1.74</v>
@@ -8354,7 +8366,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="Q37">
         <v>1.91</v>
@@ -8435,7 +8447,7 @@
         <v>3</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -8638,7 +8650,7 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>1.4</v>
@@ -8844,10 +8856,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ39">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR39">
         <v>1.45</v>
@@ -8972,7 +8984,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9050,7 +9062,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ40">
         <v>0.6</v>
@@ -9178,7 +9190,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9384,7 +9396,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9590,7 +9602,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9671,7 +9683,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ43">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -9796,7 +9808,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10414,7 +10426,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10492,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ47">
         <v>0.25</v>
@@ -10620,7 +10632,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10701,7 +10713,7 @@
         <v>3</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>1.76</v>
@@ -10907,7 +10919,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR49">
         <v>1.78</v>
@@ -11032,7 +11044,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11110,7 +11122,7 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11238,7 +11250,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11316,7 +11328,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ51">
         <v>0.8</v>
@@ -11444,7 +11456,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11522,10 +11534,10 @@
         <v>0.6</v>
       </c>
       <c r="AP52">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR52">
         <v>1.21</v>
@@ -11650,7 +11662,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11728,10 +11740,10 @@
         <v>0.25</v>
       </c>
       <c r="AP53">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -11856,7 +11868,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -11937,7 +11949,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR54">
         <v>2.31</v>
@@ -12062,7 +12074,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12474,7 +12486,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="Q57">
         <v>2.8</v>
@@ -12886,7 +12898,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13298,7 +13310,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13504,7 +13516,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13661,6 +13673,830 @@
       </c>
       <c r="BP62">
         <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7796928</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45823.45833333334</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H63" t="s">
+        <v>72</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
+        <v>133</v>
+      </c>
+      <c r="P63" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q63">
+        <v>2.85</v>
+      </c>
+      <c r="R63">
+        <v>2.11</v>
+      </c>
+      <c r="S63">
+        <v>3</v>
+      </c>
+      <c r="T63">
+        <v>1.35</v>
+      </c>
+      <c r="U63">
+        <v>3</v>
+      </c>
+      <c r="V63">
+        <v>2.6</v>
+      </c>
+      <c r="W63">
+        <v>1.42</v>
+      </c>
+      <c r="X63">
+        <v>6.5</v>
+      </c>
+      <c r="Y63">
+        <v>1.08</v>
+      </c>
+      <c r="Z63">
+        <v>2.5</v>
+      </c>
+      <c r="AA63">
+        <v>3.38</v>
+      </c>
+      <c r="AB63">
+        <v>2.47</v>
+      </c>
+      <c r="AC63">
+        <v>1.05</v>
+      </c>
+      <c r="AD63">
+        <v>10.5</v>
+      </c>
+      <c r="AE63">
+        <v>1.25</v>
+      </c>
+      <c r="AF63">
+        <v>3.9</v>
+      </c>
+      <c r="AG63">
+        <v>1.76</v>
+      </c>
+      <c r="AH63">
+        <v>1.94</v>
+      </c>
+      <c r="AI63">
+        <v>1.63</v>
+      </c>
+      <c r="AJ63">
+        <v>2.27</v>
+      </c>
+      <c r="AK63">
+        <v>1.53</v>
+      </c>
+      <c r="AL63">
+        <v>1.28</v>
+      </c>
+      <c r="AM63">
+        <v>1.4</v>
+      </c>
+      <c r="AN63">
+        <v>1.8</v>
+      </c>
+      <c r="AO63">
+        <v>0.8</v>
+      </c>
+      <c r="AP63">
+        <v>2</v>
+      </c>
+      <c r="AQ63">
+        <v>0.67</v>
+      </c>
+      <c r="AR63">
+        <v>0.93</v>
+      </c>
+      <c r="AS63">
+        <v>1.78</v>
+      </c>
+      <c r="AT63">
+        <v>2.71</v>
+      </c>
+      <c r="AU63">
+        <v>5</v>
+      </c>
+      <c r="AV63">
+        <v>6</v>
+      </c>
+      <c r="AW63">
+        <v>4</v>
+      </c>
+      <c r="AX63">
+        <v>16</v>
+      </c>
+      <c r="AY63">
+        <v>9</v>
+      </c>
+      <c r="AZ63">
+        <v>22</v>
+      </c>
+      <c r="BA63">
+        <v>2</v>
+      </c>
+      <c r="BB63">
+        <v>7</v>
+      </c>
+      <c r="BC63">
+        <v>9</v>
+      </c>
+      <c r="BD63">
+        <v>2.65</v>
+      </c>
+      <c r="BE63">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF63">
+        <v>1.61</v>
+      </c>
+      <c r="BG63">
+        <v>1.11</v>
+      </c>
+      <c r="BH63">
+        <v>5</v>
+      </c>
+      <c r="BI63">
+        <v>1.18</v>
+      </c>
+      <c r="BJ63">
+        <v>3.6</v>
+      </c>
+      <c r="BK63">
+        <v>1.42</v>
+      </c>
+      <c r="BL63">
+        <v>2.62</v>
+      </c>
+      <c r="BM63">
+        <v>1.7</v>
+      </c>
+      <c r="BN63">
+        <v>2.09</v>
+      </c>
+      <c r="BO63">
+        <v>2.1</v>
+      </c>
+      <c r="BP63">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7796929</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45823.54166666666</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s">
+        <v>70</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>2</v>
+      </c>
+      <c r="N64">
+        <v>2</v>
+      </c>
+      <c r="O64" t="s">
+        <v>85</v>
+      </c>
+      <c r="P64" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q64">
+        <v>4</v>
+      </c>
+      <c r="R64">
+        <v>2.4</v>
+      </c>
+      <c r="S64">
+        <v>2.25</v>
+      </c>
+      <c r="T64">
+        <v>1.25</v>
+      </c>
+      <c r="U64">
+        <v>3.75</v>
+      </c>
+      <c r="V64">
+        <v>2.15</v>
+      </c>
+      <c r="W64">
+        <v>1.64</v>
+      </c>
+      <c r="X64">
+        <v>4.8</v>
+      </c>
+      <c r="Y64">
+        <v>1.13</v>
+      </c>
+      <c r="Z64">
+        <v>3.5</v>
+      </c>
+      <c r="AA64">
+        <v>4.1</v>
+      </c>
+      <c r="AB64">
+        <v>1.78</v>
+      </c>
+      <c r="AC64">
+        <v>1.02</v>
+      </c>
+      <c r="AD64">
+        <v>17</v>
+      </c>
+      <c r="AE64">
+        <v>1.16</v>
+      </c>
+      <c r="AF64">
+        <v>5</v>
+      </c>
+      <c r="AG64">
+        <v>1.54</v>
+      </c>
+      <c r="AH64">
+        <v>2.5</v>
+      </c>
+      <c r="AI64">
+        <v>1.53</v>
+      </c>
+      <c r="AJ64">
+        <v>2.5</v>
+      </c>
+      <c r="AK64">
+        <v>1.2</v>
+      </c>
+      <c r="AL64">
+        <v>1.22</v>
+      </c>
+      <c r="AM64">
+        <v>1.23</v>
+      </c>
+      <c r="AN64">
+        <v>1.75</v>
+      </c>
+      <c r="AO64">
+        <v>1.5</v>
+      </c>
+      <c r="AP64">
+        <v>1.4</v>
+      </c>
+      <c r="AQ64">
+        <v>1.8</v>
+      </c>
+      <c r="AR64">
+        <v>1.25</v>
+      </c>
+      <c r="AS64">
+        <v>1.48</v>
+      </c>
+      <c r="AT64">
+        <v>2.73</v>
+      </c>
+      <c r="AU64">
+        <v>0</v>
+      </c>
+      <c r="AV64">
+        <v>7</v>
+      </c>
+      <c r="AW64">
+        <v>8</v>
+      </c>
+      <c r="AX64">
+        <v>4</v>
+      </c>
+      <c r="AY64">
+        <v>8</v>
+      </c>
+      <c r="AZ64">
+        <v>11</v>
+      </c>
+      <c r="BA64">
+        <v>8</v>
+      </c>
+      <c r="BB64">
+        <v>8</v>
+      </c>
+      <c r="BC64">
+        <v>16</v>
+      </c>
+      <c r="BD64">
+        <v>3.34</v>
+      </c>
+      <c r="BE64">
+        <v>9.6</v>
+      </c>
+      <c r="BF64">
+        <v>1.5</v>
+      </c>
+      <c r="BG64">
+        <v>1.08</v>
+      </c>
+      <c r="BH64">
+        <v>6</v>
+      </c>
+      <c r="BI64">
+        <v>1.17</v>
+      </c>
+      <c r="BJ64">
+        <v>4.15</v>
+      </c>
+      <c r="BK64">
+        <v>1.33</v>
+      </c>
+      <c r="BL64">
+        <v>3</v>
+      </c>
+      <c r="BM64">
+        <v>1.55</v>
+      </c>
+      <c r="BN64">
+        <v>2.3</v>
+      </c>
+      <c r="BO64">
+        <v>1.8</v>
+      </c>
+      <c r="BP64">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7796930</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45823.67708333334</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>73</v>
+      </c>
+      <c r="H65" t="s">
+        <v>80</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>2</v>
+      </c>
+      <c r="O65" t="s">
+        <v>134</v>
+      </c>
+      <c r="P65" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q65">
+        <v>3.3</v>
+      </c>
+      <c r="R65">
+        <v>2.3</v>
+      </c>
+      <c r="S65">
+        <v>2.62</v>
+      </c>
+      <c r="T65">
+        <v>1.26</v>
+      </c>
+      <c r="U65">
+        <v>3.8</v>
+      </c>
+      <c r="V65">
+        <v>2.2</v>
+      </c>
+      <c r="W65">
+        <v>1.66</v>
+      </c>
+      <c r="X65">
+        <v>4.55</v>
+      </c>
+      <c r="Y65">
+        <v>1.17</v>
+      </c>
+      <c r="Z65">
+        <v>3.02</v>
+      </c>
+      <c r="AA65">
+        <v>3.86</v>
+      </c>
+      <c r="AB65">
+        <v>2.17</v>
+      </c>
+      <c r="AC65">
+        <v>1.02</v>
+      </c>
+      <c r="AD65">
+        <v>12</v>
+      </c>
+      <c r="AE65">
+        <v>1.14</v>
+      </c>
+      <c r="AF65">
+        <v>5.3</v>
+      </c>
+      <c r="AG65">
+        <v>1.5</v>
+      </c>
+      <c r="AH65">
+        <v>2.5</v>
+      </c>
+      <c r="AI65">
+        <v>1.43</v>
+      </c>
+      <c r="AJ65">
+        <v>2.7</v>
+      </c>
+      <c r="AK65">
+        <v>1.29</v>
+      </c>
+      <c r="AL65">
+        <v>1.25</v>
+      </c>
+      <c r="AM65">
+        <v>1.4</v>
+      </c>
+      <c r="AN65">
+        <v>1.8</v>
+      </c>
+      <c r="AO65">
+        <v>0.5</v>
+      </c>
+      <c r="AP65">
+        <v>2</v>
+      </c>
+      <c r="AQ65">
+        <v>0.43</v>
+      </c>
+      <c r="AR65">
+        <v>1.59</v>
+      </c>
+      <c r="AS65">
+        <v>1.52</v>
+      </c>
+      <c r="AT65">
+        <v>3.11</v>
+      </c>
+      <c r="AU65">
+        <v>6</v>
+      </c>
+      <c r="AV65">
+        <v>5</v>
+      </c>
+      <c r="AW65">
+        <v>5</v>
+      </c>
+      <c r="AX65">
+        <v>11</v>
+      </c>
+      <c r="AY65">
+        <v>11</v>
+      </c>
+      <c r="AZ65">
+        <v>16</v>
+      </c>
+      <c r="BA65">
+        <v>4</v>
+      </c>
+      <c r="BB65">
+        <v>4</v>
+      </c>
+      <c r="BC65">
+        <v>8</v>
+      </c>
+      <c r="BD65">
+        <v>2.17</v>
+      </c>
+      <c r="BE65">
+        <v>7.1</v>
+      </c>
+      <c r="BF65">
+        <v>2.01</v>
+      </c>
+      <c r="BG65">
+        <v>1.13</v>
+      </c>
+      <c r="BH65">
+        <v>5</v>
+      </c>
+      <c r="BI65">
+        <v>1.23</v>
+      </c>
+      <c r="BJ65">
+        <v>3.6</v>
+      </c>
+      <c r="BK65">
+        <v>1.5</v>
+      </c>
+      <c r="BL65">
+        <v>2.62</v>
+      </c>
+      <c r="BM65">
+        <v>1.65</v>
+      </c>
+      <c r="BN65">
+        <v>2.1</v>
+      </c>
+      <c r="BO65">
+        <v>2.06</v>
+      </c>
+      <c r="BP65">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7796932</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45823.67708333334</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s">
+        <v>79</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>2</v>
+      </c>
+      <c r="L66">
+        <v>4</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>5</v>
+      </c>
+      <c r="O66" t="s">
+        <v>135</v>
+      </c>
+      <c r="P66" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q66">
+        <v>2.68</v>
+      </c>
+      <c r="R66">
+        <v>2.4</v>
+      </c>
+      <c r="S66">
+        <v>2.95</v>
+      </c>
+      <c r="T66">
+        <v>1.22</v>
+      </c>
+      <c r="U66">
+        <v>3.66</v>
+      </c>
+      <c r="V66">
+        <v>2.15</v>
+      </c>
+      <c r="W66">
+        <v>1.68</v>
+      </c>
+      <c r="X66">
+        <v>4.45</v>
+      </c>
+      <c r="Y66">
+        <v>1.18</v>
+      </c>
+      <c r="Z66">
+        <v>2.45</v>
+      </c>
+      <c r="AA66">
+        <v>3.7</v>
+      </c>
+      <c r="AB66">
+        <v>2.45</v>
+      </c>
+      <c r="AC66">
+        <v>1.03</v>
+      </c>
+      <c r="AD66">
+        <v>17</v>
+      </c>
+      <c r="AE66">
+        <v>1.1</v>
+      </c>
+      <c r="AF66">
+        <v>5.5</v>
+      </c>
+      <c r="AG66">
+        <v>1.44</v>
+      </c>
+      <c r="AH66">
+        <v>2.5</v>
+      </c>
+      <c r="AI66">
+        <v>1.42</v>
+      </c>
+      <c r="AJ66">
+        <v>2.75</v>
+      </c>
+      <c r="AK66">
+        <v>1.22</v>
+      </c>
+      <c r="AL66">
+        <v>1.25</v>
+      </c>
+      <c r="AM66">
+        <v>1.52</v>
+      </c>
+      <c r="AN66">
+        <v>2</v>
+      </c>
+      <c r="AO66">
+        <v>1</v>
+      </c>
+      <c r="AP66">
+        <v>2.17</v>
+      </c>
+      <c r="AQ66">
+        <v>0.86</v>
+      </c>
+      <c r="AR66">
+        <v>1.5</v>
+      </c>
+      <c r="AS66">
+        <v>1.71</v>
+      </c>
+      <c r="AT66">
+        <v>3.21</v>
+      </c>
+      <c r="AU66">
+        <v>7</v>
+      </c>
+      <c r="AV66">
+        <v>3</v>
+      </c>
+      <c r="AW66">
+        <v>5</v>
+      </c>
+      <c r="AX66">
+        <v>7</v>
+      </c>
+      <c r="AY66">
+        <v>12</v>
+      </c>
+      <c r="AZ66">
+        <v>10</v>
+      </c>
+      <c r="BA66">
+        <v>7</v>
+      </c>
+      <c r="BB66">
+        <v>3</v>
+      </c>
+      <c r="BC66">
+        <v>10</v>
+      </c>
+      <c r="BD66">
+        <v>1.65</v>
+      </c>
+      <c r="BE66">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF66">
+        <v>2.52</v>
+      </c>
+      <c r="BG66">
+        <v>1.11</v>
+      </c>
+      <c r="BH66">
+        <v>5.25</v>
+      </c>
+      <c r="BI66">
+        <v>1.25</v>
+      </c>
+      <c r="BJ66">
+        <v>3.6</v>
+      </c>
+      <c r="BK66">
+        <v>1.41</v>
+      </c>
+      <c r="BL66">
+        <v>2.7</v>
+      </c>
+      <c r="BM66">
+        <v>1.65</v>
+      </c>
+      <c r="BN66">
+        <v>2.1</v>
+      </c>
+      <c r="BO66">
+        <v>2</v>
+      </c>
+      <c r="BP66">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="177">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -418,10 +418,13 @@
     <t>['35']</t>
   </si>
   <si>
-    <t>['76', '6']</t>
-  </si>
-  <si>
-    <t>['71', '85', '90+1', '33']</t>
+    <t>['77', '6']</t>
+  </si>
+  <si>
+    <t>['71', '84', '90', '33']</t>
+  </si>
+  <si>
+    <t>['12', '43', '49']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -539,6 +542,9 @@
   </si>
   <si>
     <t>['17']</t>
+  </si>
+  <si>
+    <t>['30', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -900,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP66"/>
+  <dimension ref="A1:BP67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1362,7 +1368,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1568,7 +1574,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1649,7 +1655,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1774,7 +1780,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2186,7 +2192,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -3010,7 +3016,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3422,7 +3428,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3628,7 +3634,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3834,7 +3840,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4040,7 +4046,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4121,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4246,7 +4252,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4452,7 +4458,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4864,7 +4870,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5070,7 +5076,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5482,7 +5488,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5894,7 +5900,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6100,7 +6106,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6924,7 +6930,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7005,7 +7011,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ30">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>2.63</v>
@@ -7130,7 +7136,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7542,7 +7548,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7748,7 +7754,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8160,7 +8166,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8984,7 +8990,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9065,7 +9071,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ40">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR40">
         <v>1.47</v>
@@ -9190,7 +9196,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9396,7 +9402,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9602,7 +9608,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9808,7 +9814,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10426,7 +10432,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10632,7 +10638,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11044,7 +11050,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11250,7 +11256,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11456,7 +11462,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11662,7 +11668,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11868,7 +11874,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12074,7 +12080,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12155,7 +12161,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ55">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>1.56</v>
@@ -12898,7 +12904,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13310,7 +13316,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13516,7 +13522,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13928,7 +13934,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14227,22 +14233,22 @@
         <v>3.11</v>
       </c>
       <c r="AU65">
+        <v>7</v>
+      </c>
+      <c r="AV65">
         <v>6</v>
       </c>
-      <c r="AV65">
-        <v>5</v>
-      </c>
       <c r="AW65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX65">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY65">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ65">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA65">
         <v>4</v>
@@ -14340,7 +14346,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14497,6 +14503,212 @@
       </c>
       <c r="BP66">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7796931</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45824.67708333334</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>74</v>
+      </c>
+      <c r="H67" t="s">
+        <v>78</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67">
+        <v>4</v>
+      </c>
+      <c r="L67">
+        <v>3</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67">
+        <v>5</v>
+      </c>
+      <c r="O67" t="s">
+        <v>136</v>
+      </c>
+      <c r="P67" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q67">
+        <v>2.04</v>
+      </c>
+      <c r="R67">
+        <v>2.95</v>
+      </c>
+      <c r="S67">
+        <v>3.45</v>
+      </c>
+      <c r="T67">
+        <v>1.14</v>
+      </c>
+      <c r="U67">
+        <v>5.5</v>
+      </c>
+      <c r="V67">
+        <v>1.65</v>
+      </c>
+      <c r="W67">
+        <v>2.1</v>
+      </c>
+      <c r="X67">
+        <v>3.15</v>
+      </c>
+      <c r="Y67">
+        <v>1.3</v>
+      </c>
+      <c r="Z67">
+        <v>1.57</v>
+      </c>
+      <c r="AA67">
+        <v>4.85</v>
+      </c>
+      <c r="AB67">
+        <v>4</v>
+      </c>
+      <c r="AC67">
+        <v>1.01</v>
+      </c>
+      <c r="AD67">
+        <v>29</v>
+      </c>
+      <c r="AE67">
+        <v>1.05</v>
+      </c>
+      <c r="AF67">
+        <v>11</v>
+      </c>
+      <c r="AG67">
+        <v>1.18</v>
+      </c>
+      <c r="AH67">
+        <v>4.4</v>
+      </c>
+      <c r="AI67">
+        <v>1.29</v>
+      </c>
+      <c r="AJ67">
+        <v>3.63</v>
+      </c>
+      <c r="AK67">
+        <v>1.15</v>
+      </c>
+      <c r="AL67">
+        <v>1.18</v>
+      </c>
+      <c r="AM67">
+        <v>2.17</v>
+      </c>
+      <c r="AN67">
+        <v>3</v>
+      </c>
+      <c r="AO67">
+        <v>0.6</v>
+      </c>
+      <c r="AP67">
+        <v>3</v>
+      </c>
+      <c r="AQ67">
+        <v>0.5</v>
+      </c>
+      <c r="AR67">
+        <v>1.75</v>
+      </c>
+      <c r="AS67">
+        <v>1.93</v>
+      </c>
+      <c r="AT67">
+        <v>3.68</v>
+      </c>
+      <c r="AU67">
+        <v>4</v>
+      </c>
+      <c r="AV67">
+        <v>5</v>
+      </c>
+      <c r="AW67">
+        <v>1</v>
+      </c>
+      <c r="AX67">
+        <v>4</v>
+      </c>
+      <c r="AY67">
+        <v>5</v>
+      </c>
+      <c r="AZ67">
+        <v>9</v>
+      </c>
+      <c r="BA67">
+        <v>7</v>
+      </c>
+      <c r="BB67">
+        <v>5</v>
+      </c>
+      <c r="BC67">
+        <v>12</v>
+      </c>
+      <c r="BD67">
+        <v>1.51</v>
+      </c>
+      <c r="BE67">
+        <v>7.8</v>
+      </c>
+      <c r="BF67">
+        <v>2.94</v>
+      </c>
+      <c r="BG67">
+        <v>1.08</v>
+      </c>
+      <c r="BH67">
+        <v>6</v>
+      </c>
+      <c r="BI67">
+        <v>1.18</v>
+      </c>
+      <c r="BJ67">
+        <v>4.33</v>
+      </c>
+      <c r="BK67">
+        <v>1.27</v>
+      </c>
+      <c r="BL67">
+        <v>3</v>
+      </c>
+      <c r="BM67">
+        <v>1.53</v>
+      </c>
+      <c r="BN67">
+        <v>2.45</v>
+      </c>
+      <c r="BO67">
+        <v>1.83</v>
+      </c>
+      <c r="BP67">
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -544,7 +544,7 @@
     <t>['17']</t>
   </si>
   <si>
-    <t>['30', '45+1']</t>
+    <t>['30', '45']</t>
   </si>
 </sst>
 </file>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="180">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,6 +427,9 @@
     <t>['12', '43', '49']</t>
   </si>
   <si>
+    <t>['32', '48']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -545,6 +548,12 @@
   </si>
   <si>
     <t>['30', '45']</t>
+  </si>
+  <si>
+    <t>['29', '69']</t>
+  </si>
+  <si>
+    <t>['42', '53', '51']</t>
   </si>
 </sst>
 </file>
@@ -906,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP67"/>
+  <dimension ref="A1:BP70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1368,7 +1377,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1449,7 +1458,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ3">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1574,7 +1583,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1652,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -1780,7 +1789,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2192,7 +2201,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -3016,7 +3025,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3428,7 +3437,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3634,7 +3643,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3840,7 +3849,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -3918,10 +3927,10 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ15">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4046,7 +4055,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4124,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ16">
         <v>0.5</v>
@@ -4252,7 +4261,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4333,7 +4342,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ17">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR17">
         <v>2.7</v>
@@ -4458,7 +4467,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4745,7 +4754,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
         <v>1.5</v>
@@ -4870,7 +4879,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5076,7 +5085,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5154,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>0.43</v>
@@ -5488,7 +5497,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5900,7 +5909,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -5981,7 +5990,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>2.26</v>
@@ -6106,7 +6115,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6187,7 +6196,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6390,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ27">
         <v>0.67</v>
@@ -6596,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ28">
         <v>0.8</v>
@@ -6805,7 +6814,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ29">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR29">
         <v>1.52</v>
@@ -6930,7 +6939,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7136,7 +7145,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7548,7 +7557,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7754,7 +7763,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8166,7 +8175,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8244,7 +8253,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36">
         <v>1.8</v>
@@ -8659,7 +8668,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR38">
         <v>1.74</v>
@@ -8990,7 +8999,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9196,7 +9205,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9277,7 +9286,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1.56</v>
@@ -9402,7 +9411,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9608,7 +9617,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9686,7 +9695,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ43">
         <v>0.43</v>
@@ -9814,7 +9823,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10304,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46">
         <v>0.2</v>
@@ -10432,7 +10441,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10513,7 +10522,7 @@
         <v>2</v>
       </c>
       <c r="AQ47">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR47">
         <v>0.74</v>
@@ -10638,7 +10647,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10922,7 +10931,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ49">
         <v>1.8</v>
@@ -11050,7 +11059,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11131,7 +11140,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
         <v>0.79</v>
@@ -11256,7 +11265,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11462,7 +11471,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11668,7 +11677,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11874,7 +11883,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12080,7 +12089,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12367,7 +12376,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR56">
         <v>1.86</v>
@@ -12570,10 +12579,10 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ57">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -12776,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ58">
         <v>0.2</v>
@@ -12904,7 +12913,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -12982,7 +12991,7 @@
         <v>0.8</v>
       </c>
       <c r="AP59">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ59">
         <v>1.17</v>
@@ -13191,7 +13200,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>2.23</v>
@@ -13316,7 +13325,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13522,7 +13531,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13934,7 +13943,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14346,7 +14355,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14552,7 +14561,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14708,6 +14717,624 @@
         <v>1.83</v>
       </c>
       <c r="BP67">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7796934</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45830.45833333334</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s">
+        <v>76</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>2</v>
+      </c>
+      <c r="O68" t="s">
+        <v>137</v>
+      </c>
+      <c r="P68" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q68">
+        <v>2.19</v>
+      </c>
+      <c r="R68">
+        <v>2.35</v>
+      </c>
+      <c r="S68">
+        <v>4.5</v>
+      </c>
+      <c r="T68">
+        <v>1.3</v>
+      </c>
+      <c r="U68">
+        <v>3.2</v>
+      </c>
+      <c r="V68">
+        <v>2.33</v>
+      </c>
+      <c r="W68">
+        <v>1.55</v>
+      </c>
+      <c r="X68">
+        <v>5.3</v>
+      </c>
+      <c r="Y68">
+        <v>1.11</v>
+      </c>
+      <c r="Z68">
+        <v>1.64</v>
+      </c>
+      <c r="AA68">
+        <v>3.8</v>
+      </c>
+      <c r="AB68">
+        <v>4.4</v>
+      </c>
+      <c r="AC68">
+        <v>1.04</v>
+      </c>
+      <c r="AD68">
+        <v>13</v>
+      </c>
+      <c r="AE68">
+        <v>1.22</v>
+      </c>
+      <c r="AF68">
+        <v>4.4</v>
+      </c>
+      <c r="AG68">
+        <v>1.61</v>
+      </c>
+      <c r="AH68">
+        <v>2.1</v>
+      </c>
+      <c r="AI68">
+        <v>1.6</v>
+      </c>
+      <c r="AJ68">
+        <v>2.1</v>
+      </c>
+      <c r="AK68">
+        <v>1.25</v>
+      </c>
+      <c r="AL68">
+        <v>1.23</v>
+      </c>
+      <c r="AM68">
+        <v>2.15</v>
+      </c>
+      <c r="AN68">
+        <v>2</v>
+      </c>
+      <c r="AO68">
+        <v>1.4</v>
+      </c>
+      <c r="AP68">
+        <v>2.2</v>
+      </c>
+      <c r="AQ68">
+        <v>1.17</v>
+      </c>
+      <c r="AR68">
+        <v>1.56</v>
+      </c>
+      <c r="AS68">
+        <v>1.18</v>
+      </c>
+      <c r="AT68">
+        <v>2.74</v>
+      </c>
+      <c r="AU68">
+        <v>6</v>
+      </c>
+      <c r="AV68">
+        <v>2</v>
+      </c>
+      <c r="AW68">
+        <v>10</v>
+      </c>
+      <c r="AX68">
+        <v>4</v>
+      </c>
+      <c r="AY68">
+        <v>16</v>
+      </c>
+      <c r="AZ68">
+        <v>6</v>
+      </c>
+      <c r="BA68">
+        <v>7</v>
+      </c>
+      <c r="BB68">
+        <v>1</v>
+      </c>
+      <c r="BC68">
+        <v>8</v>
+      </c>
+      <c r="BD68">
+        <v>1.35</v>
+      </c>
+      <c r="BE68">
+        <v>10.25</v>
+      </c>
+      <c r="BF68">
+        <v>3.74</v>
+      </c>
+      <c r="BG68">
+        <v>1.13</v>
+      </c>
+      <c r="BH68">
+        <v>5</v>
+      </c>
+      <c r="BI68">
+        <v>1.25</v>
+      </c>
+      <c r="BJ68">
+        <v>3.6</v>
+      </c>
+      <c r="BK68">
+        <v>1.42</v>
+      </c>
+      <c r="BL68">
+        <v>2.62</v>
+      </c>
+      <c r="BM68">
+        <v>1.77</v>
+      </c>
+      <c r="BN68">
+        <v>1.95</v>
+      </c>
+      <c r="BO68">
+        <v>2.1</v>
+      </c>
+      <c r="BP68">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7796935</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45830.67708333334</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>72</v>
+      </c>
+      <c r="H69" t="s">
+        <v>74</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+      <c r="N69">
+        <v>2</v>
+      </c>
+      <c r="O69" t="s">
+        <v>85</v>
+      </c>
+      <c r="P69" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q69">
+        <v>3.1</v>
+      </c>
+      <c r="R69">
+        <v>2.45</v>
+      </c>
+      <c r="S69">
+        <v>2.38</v>
+      </c>
+      <c r="T69">
+        <v>1.22</v>
+      </c>
+      <c r="U69">
+        <v>3.8</v>
+      </c>
+      <c r="V69">
+        <v>2.05</v>
+      </c>
+      <c r="W69">
+        <v>1.67</v>
+      </c>
+      <c r="X69">
+        <v>4.5</v>
+      </c>
+      <c r="Y69">
+        <v>1.18</v>
+      </c>
+      <c r="Z69">
+        <v>3.26</v>
+      </c>
+      <c r="AA69">
+        <v>3.63</v>
+      </c>
+      <c r="AB69">
+        <v>1.93</v>
+      </c>
+      <c r="AC69">
+        <v>1.01</v>
+      </c>
+      <c r="AD69">
+        <v>19</v>
+      </c>
+      <c r="AE69">
+        <v>1.14</v>
+      </c>
+      <c r="AF69">
+        <v>5.7</v>
+      </c>
+      <c r="AG69">
+        <v>1.5</v>
+      </c>
+      <c r="AH69">
+        <v>2.41</v>
+      </c>
+      <c r="AI69">
+        <v>1.42</v>
+      </c>
+      <c r="AJ69">
+        <v>2.62</v>
+      </c>
+      <c r="AK69">
+        <v>1.25</v>
+      </c>
+      <c r="AL69">
+        <v>1.27</v>
+      </c>
+      <c r="AM69">
+        <v>1.33</v>
+      </c>
+      <c r="AN69">
+        <v>1.6</v>
+      </c>
+      <c r="AO69">
+        <v>1</v>
+      </c>
+      <c r="AP69">
+        <v>1.33</v>
+      </c>
+      <c r="AQ69">
+        <v>1.33</v>
+      </c>
+      <c r="AR69">
+        <v>1.56</v>
+      </c>
+      <c r="AS69">
+        <v>1.5</v>
+      </c>
+      <c r="AT69">
+        <v>3.06</v>
+      </c>
+      <c r="AU69">
+        <v>4</v>
+      </c>
+      <c r="AV69">
+        <v>6</v>
+      </c>
+      <c r="AW69">
+        <v>10</v>
+      </c>
+      <c r="AX69">
+        <v>3</v>
+      </c>
+      <c r="AY69">
+        <v>14</v>
+      </c>
+      <c r="AZ69">
+        <v>9</v>
+      </c>
+      <c r="BA69">
+        <v>9</v>
+      </c>
+      <c r="BB69">
+        <v>4</v>
+      </c>
+      <c r="BC69">
+        <v>13</v>
+      </c>
+      <c r="BD69">
+        <v>2.34</v>
+      </c>
+      <c r="BE69">
+        <v>6.85</v>
+      </c>
+      <c r="BF69">
+        <v>1.88</v>
+      </c>
+      <c r="BG69">
+        <v>1.09</v>
+      </c>
+      <c r="BH69">
+        <v>5.65</v>
+      </c>
+      <c r="BI69">
+        <v>1.19</v>
+      </c>
+      <c r="BJ69">
+        <v>3.8</v>
+      </c>
+      <c r="BK69">
+        <v>1.43</v>
+      </c>
+      <c r="BL69">
+        <v>2.9</v>
+      </c>
+      <c r="BM69">
+        <v>1.55</v>
+      </c>
+      <c r="BN69">
+        <v>2.2</v>
+      </c>
+      <c r="BO69">
+        <v>1.9</v>
+      </c>
+      <c r="BP69">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7796936</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45830.67708333334</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s">
+        <v>75</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>3</v>
+      </c>
+      <c r="N70">
+        <v>3</v>
+      </c>
+      <c r="O70" t="s">
+        <v>85</v>
+      </c>
+      <c r="P70" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q70">
+        <v>3.05</v>
+      </c>
+      <c r="R70">
+        <v>2.5</v>
+      </c>
+      <c r="S70">
+        <v>2.78</v>
+      </c>
+      <c r="T70">
+        <v>1.17</v>
+      </c>
+      <c r="U70">
+        <v>4.33</v>
+      </c>
+      <c r="V70">
+        <v>1.94</v>
+      </c>
+      <c r="W70">
+        <v>1.82</v>
+      </c>
+      <c r="X70">
+        <v>3.85</v>
+      </c>
+      <c r="Y70">
+        <v>1.22</v>
+      </c>
+      <c r="Z70">
+        <v>2.65</v>
+      </c>
+      <c r="AA70">
+        <v>4.01</v>
+      </c>
+      <c r="AB70">
+        <v>2.18</v>
+      </c>
+      <c r="AC70">
+        <v>1.01</v>
+      </c>
+      <c r="AD70">
+        <v>18</v>
+      </c>
+      <c r="AE70">
+        <v>1.08</v>
+      </c>
+      <c r="AF70">
+        <v>6.46</v>
+      </c>
+      <c r="AG70">
+        <v>1.36</v>
+      </c>
+      <c r="AH70">
+        <v>3</v>
+      </c>
+      <c r="AI70">
+        <v>1.35</v>
+      </c>
+      <c r="AJ70">
+        <v>3</v>
+      </c>
+      <c r="AK70">
+        <v>1.62</v>
+      </c>
+      <c r="AL70">
+        <v>1.24</v>
+      </c>
+      <c r="AM70">
+        <v>1.44</v>
+      </c>
+      <c r="AN70">
+        <v>0.75</v>
+      </c>
+      <c r="AO70">
+        <v>0.25</v>
+      </c>
+      <c r="AP70">
+        <v>0.6</v>
+      </c>
+      <c r="AQ70">
+        <v>0.8</v>
+      </c>
+      <c r="AR70">
+        <v>1.61</v>
+      </c>
+      <c r="AS70">
+        <v>1.32</v>
+      </c>
+      <c r="AT70">
+        <v>2.93</v>
+      </c>
+      <c r="AU70">
+        <v>5</v>
+      </c>
+      <c r="AV70">
+        <v>9</v>
+      </c>
+      <c r="AW70">
+        <v>8</v>
+      </c>
+      <c r="AX70">
+        <v>14</v>
+      </c>
+      <c r="AY70">
+        <v>13</v>
+      </c>
+      <c r="AZ70">
+        <v>23</v>
+      </c>
+      <c r="BA70">
+        <v>10</v>
+      </c>
+      <c r="BB70">
+        <v>7</v>
+      </c>
+      <c r="BC70">
+        <v>17</v>
+      </c>
+      <c r="BD70">
+        <v>2.25</v>
+      </c>
+      <c r="BE70">
+        <v>7</v>
+      </c>
+      <c r="BF70">
+        <v>1.93</v>
+      </c>
+      <c r="BG70">
+        <v>0</v>
+      </c>
+      <c r="BH70">
+        <v>0</v>
+      </c>
+      <c r="BI70">
+        <v>1.12</v>
+      </c>
+      <c r="BJ70">
+        <v>4.9</v>
+      </c>
+      <c r="BK70">
+        <v>1.19</v>
+      </c>
+      <c r="BL70">
+        <v>3.52</v>
+      </c>
+      <c r="BM70">
+        <v>1.43</v>
+      </c>
+      <c r="BN70">
+        <v>2.63</v>
+      </c>
+      <c r="BO70">
+        <v>1.62</v>
+      </c>
+      <c r="BP70">
         <v>1.91</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="184">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -430,6 +430,15 @@
     <t>['32', '48']</t>
   </si>
   <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['6', '27', '44', '70', '75', '90+5']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -439,9 +448,6 @@
     <t>['27']</t>
   </si>
   <si>
-    <t>['90']</t>
-  </si>
-  <si>
     <t>['17', '38']</t>
   </si>
   <si>
@@ -550,10 +556,16 @@
     <t>['30', '45']</t>
   </si>
   <si>
-    <t>['29', '69']</t>
-  </si>
-  <si>
-    <t>['42', '53', '51']</t>
+    <t>['69', '30']</t>
+  </si>
+  <si>
+    <t>['41', '53', '50']</t>
+  </si>
+  <si>
+    <t>['54', '55']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
 </sst>
 </file>
@@ -915,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP70"/>
+  <dimension ref="A1:BP73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1249,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1377,7 +1389,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1455,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ3">
         <v>1.17</v>
@@ -1583,7 +1595,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1664,7 +1676,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1789,7 +1801,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2201,7 +2213,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q7">
         <v>2.6</v>
@@ -3025,7 +3037,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3437,7 +3449,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3643,7 +3655,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3721,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ14">
         <v>0.67</v>
@@ -3849,7 +3861,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4055,7 +4067,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4136,7 +4148,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4261,7 +4273,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4339,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>0.8</v>
@@ -4467,7 +4479,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4545,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4879,7 +4891,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5085,7 +5097,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5497,7 +5509,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5784,7 +5796,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AR24">
         <v>1.52</v>
@@ -5909,7 +5921,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -5987,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ25">
         <v>1.33</v>
@@ -6115,7 +6127,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6193,7 +6205,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
         <v>1.17</v>
@@ -6939,7 +6951,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7017,10 +7029,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR30">
         <v>2.63</v>
@@ -7145,7 +7157,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7226,7 +7238,7 @@
         <v>3</v>
       </c>
       <c r="AQ31">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR31">
         <v>2.21</v>
@@ -7432,7 +7444,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>0.75</v>
@@ -7557,7 +7569,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7763,7 +7775,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -7841,7 +7853,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ34">
         <v>0.86</v>
@@ -8050,7 +8062,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ35">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR35">
         <v>1.56</v>
@@ -8175,7 +8187,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8871,7 +8883,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ39">
         <v>0.67</v>
@@ -8999,7 +9011,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9080,7 +9092,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR40">
         <v>1.47</v>
@@ -9205,7 +9217,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9411,7 +9423,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9489,7 +9501,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>0.8</v>
@@ -9617,7 +9629,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9823,7 +9835,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -9904,7 +9916,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR44">
         <v>1.64</v>
@@ -10107,7 +10119,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ45">
         <v>1.17</v>
@@ -10316,7 +10328,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AR46">
         <v>1.53</v>
@@ -10441,7 +10453,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10647,7 +10659,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11059,7 +11071,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11265,7 +11277,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11471,7 +11483,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11549,7 +11561,7 @@
         <v>0.6</v>
       </c>
       <c r="AP52">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ52">
         <v>0.43</v>
@@ -11677,7 +11689,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11883,7 +11895,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -11961,7 +11973,7 @@
         <v>0.6</v>
       </c>
       <c r="AP54">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>0.86</v>
@@ -12089,7 +12101,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12170,7 +12182,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR55">
         <v>1.56</v>
@@ -12788,7 +12800,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ58">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -12913,7 +12925,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13197,7 +13209,7 @@
         <v>1.25</v>
       </c>
       <c r="AP60">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1.33</v>
@@ -13325,7 +13337,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13403,10 +13415,10 @@
         <v>0.75</v>
       </c>
       <c r="AP61">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ61">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR61">
         <v>2.25</v>
@@ -13531,7 +13543,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13943,7 +13955,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14021,7 +14033,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
         <v>1.8</v>
@@ -14355,7 +14367,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14561,7 +14573,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14642,7 +14654,7 @@
         <v>3</v>
       </c>
       <c r="AQ67">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR67">
         <v>1.75</v>
@@ -14866,13 +14878,13 @@
         <v>2</v>
       </c>
       <c r="AW68">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX68">
         <v>4</v>
       </c>
       <c r="AY68">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ68">
         <v>6</v>
@@ -14973,7 +14985,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15066,22 +15078,22 @@
         <v>3.06</v>
       </c>
       <c r="AU69">
+        <v>2</v>
+      </c>
+      <c r="AV69">
         <v>4</v>
       </c>
-      <c r="AV69">
+      <c r="AW69">
         <v>6</v>
-      </c>
-      <c r="AW69">
-        <v>10</v>
       </c>
       <c r="AX69">
         <v>3</v>
       </c>
       <c r="AY69">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ69">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA69">
         <v>9</v>
@@ -15179,7 +15191,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15275,19 +15287,19 @@
         <v>5</v>
       </c>
       <c r="AV70">
+        <v>8</v>
+      </c>
+      <c r="AW70">
+        <v>4</v>
+      </c>
+      <c r="AX70">
+        <v>6</v>
+      </c>
+      <c r="AY70">
         <v>9</v>
       </c>
-      <c r="AW70">
-        <v>8</v>
-      </c>
-      <c r="AX70">
+      <c r="AZ70">
         <v>14</v>
-      </c>
-      <c r="AY70">
-        <v>13</v>
-      </c>
-      <c r="AZ70">
-        <v>23</v>
       </c>
       <c r="BA70">
         <v>10</v>
@@ -15336,6 +15348,624 @@
       </c>
       <c r="BP70">
         <v>1.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7796938</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45831.625</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s">
+        <v>77</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>2</v>
+      </c>
+      <c r="N71">
+        <v>3</v>
+      </c>
+      <c r="O71" t="s">
+        <v>138</v>
+      </c>
+      <c r="P71" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q71">
+        <v>2.61</v>
+      </c>
+      <c r="R71">
+        <v>2.23</v>
+      </c>
+      <c r="S71">
+        <v>3.8</v>
+      </c>
+      <c r="T71">
+        <v>1.28</v>
+      </c>
+      <c r="U71">
+        <v>3.3</v>
+      </c>
+      <c r="V71">
+        <v>2.46</v>
+      </c>
+      <c r="W71">
+        <v>1.52</v>
+      </c>
+      <c r="X71">
+        <v>5.5</v>
+      </c>
+      <c r="Y71">
+        <v>1.12</v>
+      </c>
+      <c r="Z71">
+        <v>2.16</v>
+      </c>
+      <c r="AA71">
+        <v>3.5</v>
+      </c>
+      <c r="AB71">
+        <v>2.98</v>
+      </c>
+      <c r="AC71">
+        <v>1.04</v>
+      </c>
+      <c r="AD71">
+        <v>12</v>
+      </c>
+      <c r="AE71">
+        <v>1.19</v>
+      </c>
+      <c r="AF71">
+        <v>4</v>
+      </c>
+      <c r="AG71">
+        <v>1.67</v>
+      </c>
+      <c r="AH71">
+        <v>2.09</v>
+      </c>
+      <c r="AI71">
+        <v>1.61</v>
+      </c>
+      <c r="AJ71">
+        <v>2.15</v>
+      </c>
+      <c r="AK71">
+        <v>1.23</v>
+      </c>
+      <c r="AL71">
+        <v>1.28</v>
+      </c>
+      <c r="AM71">
+        <v>1.79</v>
+      </c>
+      <c r="AN71">
+        <v>1.4</v>
+      </c>
+      <c r="AO71">
+        <v>0.2</v>
+      </c>
+      <c r="AP71">
+        <v>1.17</v>
+      </c>
+      <c r="AQ71">
+        <v>0.67</v>
+      </c>
+      <c r="AR71">
+        <v>1.16</v>
+      </c>
+      <c r="AS71">
+        <v>1.43</v>
+      </c>
+      <c r="AT71">
+        <v>2.59</v>
+      </c>
+      <c r="AU71">
+        <v>5</v>
+      </c>
+      <c r="AV71">
+        <v>7</v>
+      </c>
+      <c r="AW71">
+        <v>5</v>
+      </c>
+      <c r="AX71">
+        <v>1</v>
+      </c>
+      <c r="AY71">
+        <v>10</v>
+      </c>
+      <c r="AZ71">
+        <v>8</v>
+      </c>
+      <c r="BA71">
+        <v>6</v>
+      </c>
+      <c r="BB71">
+        <v>5</v>
+      </c>
+      <c r="BC71">
+        <v>11</v>
+      </c>
+      <c r="BD71">
+        <v>1.65</v>
+      </c>
+      <c r="BE71">
+        <v>7.8</v>
+      </c>
+      <c r="BF71">
+        <v>2.81</v>
+      </c>
+      <c r="BG71">
+        <v>1.11</v>
+      </c>
+      <c r="BH71">
+        <v>5.5</v>
+      </c>
+      <c r="BI71">
+        <v>1.25</v>
+      </c>
+      <c r="BJ71">
+        <v>3.6</v>
+      </c>
+      <c r="BK71">
+        <v>1.38</v>
+      </c>
+      <c r="BL71">
+        <v>2.8</v>
+      </c>
+      <c r="BM71">
+        <v>1.58</v>
+      </c>
+      <c r="BN71">
+        <v>2.23</v>
+      </c>
+      <c r="BO71">
+        <v>1.96</v>
+      </c>
+      <c r="BP71">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7796939</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45831.67708333334</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>71</v>
+      </c>
+      <c r="H72" t="s">
+        <v>78</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>6</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>7</v>
+      </c>
+      <c r="O72" t="s">
+        <v>139</v>
+      </c>
+      <c r="P72" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q72">
+        <v>2.36</v>
+      </c>
+      <c r="R72">
+        <v>2.66</v>
+      </c>
+      <c r="S72">
+        <v>3.1</v>
+      </c>
+      <c r="T72">
+        <v>1.12</v>
+      </c>
+      <c r="U72">
+        <v>5.2</v>
+      </c>
+      <c r="V72">
+        <v>1.66</v>
+      </c>
+      <c r="W72">
+        <v>2.14</v>
+      </c>
+      <c r="X72">
+        <v>2.93</v>
+      </c>
+      <c r="Y72">
+        <v>1.35</v>
+      </c>
+      <c r="Z72">
+        <v>1.64</v>
+      </c>
+      <c r="AA72">
+        <v>4.75</v>
+      </c>
+      <c r="AB72">
+        <v>4.1</v>
+      </c>
+      <c r="AC72">
+        <v>1</v>
+      </c>
+      <c r="AD72">
+        <v>23</v>
+      </c>
+      <c r="AE72">
+        <v>1.01</v>
+      </c>
+      <c r="AF72">
+        <v>10</v>
+      </c>
+      <c r="AG72">
+        <v>1.2</v>
+      </c>
+      <c r="AH72">
+        <v>4.2</v>
+      </c>
+      <c r="AI72">
+        <v>1.2</v>
+      </c>
+      <c r="AJ72">
+        <v>3.9</v>
+      </c>
+      <c r="AK72">
+        <v>1.33</v>
+      </c>
+      <c r="AL72">
+        <v>1.18</v>
+      </c>
+      <c r="AM72">
+        <v>1.85</v>
+      </c>
+      <c r="AN72">
+        <v>2.33</v>
+      </c>
+      <c r="AO72">
+        <v>0.5</v>
+      </c>
+      <c r="AP72">
+        <v>2.43</v>
+      </c>
+      <c r="AQ72">
+        <v>0.43</v>
+      </c>
+      <c r="AR72">
+        <v>2.2</v>
+      </c>
+      <c r="AS72">
+        <v>1.88</v>
+      </c>
+      <c r="AT72">
+        <v>4.08</v>
+      </c>
+      <c r="AU72">
+        <v>10</v>
+      </c>
+      <c r="AV72">
+        <v>5</v>
+      </c>
+      <c r="AW72">
+        <v>5</v>
+      </c>
+      <c r="AX72">
+        <v>9</v>
+      </c>
+      <c r="AY72">
+        <v>15</v>
+      </c>
+      <c r="AZ72">
+        <v>14</v>
+      </c>
+      <c r="BA72">
+        <v>6</v>
+      </c>
+      <c r="BB72">
+        <v>5</v>
+      </c>
+      <c r="BC72">
+        <v>11</v>
+      </c>
+      <c r="BD72">
+        <v>1.7</v>
+      </c>
+      <c r="BE72">
+        <v>7.8</v>
+      </c>
+      <c r="BF72">
+        <v>2.56</v>
+      </c>
+      <c r="BG72">
+        <v>1.08</v>
+      </c>
+      <c r="BH72">
+        <v>5.93</v>
+      </c>
+      <c r="BI72">
+        <v>1.16</v>
+      </c>
+      <c r="BJ72">
+        <v>4.4</v>
+      </c>
+      <c r="BK72">
+        <v>1.35</v>
+      </c>
+      <c r="BL72">
+        <v>3.45</v>
+      </c>
+      <c r="BM72">
+        <v>1.5</v>
+      </c>
+      <c r="BN72">
+        <v>2.4</v>
+      </c>
+      <c r="BO72">
+        <v>1.8</v>
+      </c>
+      <c r="BP72">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7796937</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45831.67708333334</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>70</v>
+      </c>
+      <c r="H73" t="s">
+        <v>73</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73" t="s">
+        <v>140</v>
+      </c>
+      <c r="P73" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q73">
+        <v>2.17</v>
+      </c>
+      <c r="R73">
+        <v>2.5</v>
+      </c>
+      <c r="S73">
+        <v>4.2</v>
+      </c>
+      <c r="T73">
+        <v>1.2</v>
+      </c>
+      <c r="U73">
+        <v>3.9</v>
+      </c>
+      <c r="V73">
+        <v>2.03</v>
+      </c>
+      <c r="W73">
+        <v>1.83</v>
+      </c>
+      <c r="X73">
+        <v>3.9</v>
+      </c>
+      <c r="Y73">
+        <v>1.2</v>
+      </c>
+      <c r="Z73">
+        <v>1.62</v>
+      </c>
+      <c r="AA73">
+        <v>4</v>
+      </c>
+      <c r="AB73">
+        <v>4.14</v>
+      </c>
+      <c r="AC73">
+        <v>1.01</v>
+      </c>
+      <c r="AD73">
+        <v>19</v>
+      </c>
+      <c r="AE73">
+        <v>1.07</v>
+      </c>
+      <c r="AF73">
+        <v>6.5</v>
+      </c>
+      <c r="AG73">
+        <v>1.32</v>
+      </c>
+      <c r="AH73">
+        <v>2.8</v>
+      </c>
+      <c r="AI73">
+        <v>1.37</v>
+      </c>
+      <c r="AJ73">
+        <v>2.8</v>
+      </c>
+      <c r="AK73">
+        <v>1.18</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>2.15</v>
+      </c>
+      <c r="AN73">
+        <v>2.17</v>
+      </c>
+      <c r="AO73">
+        <v>0.6</v>
+      </c>
+      <c r="AP73">
+        <v>2</v>
+      </c>
+      <c r="AQ73">
+        <v>0.67</v>
+      </c>
+      <c r="AR73">
+        <v>2.14</v>
+      </c>
+      <c r="AS73">
+        <v>1.28</v>
+      </c>
+      <c r="AT73">
+        <v>3.42</v>
+      </c>
+      <c r="AU73">
+        <v>4</v>
+      </c>
+      <c r="AV73">
+        <v>6</v>
+      </c>
+      <c r="AW73">
+        <v>11</v>
+      </c>
+      <c r="AX73">
+        <v>9</v>
+      </c>
+      <c r="AY73">
+        <v>15</v>
+      </c>
+      <c r="AZ73">
+        <v>15</v>
+      </c>
+      <c r="BA73">
+        <v>7</v>
+      </c>
+      <c r="BB73">
+        <v>2</v>
+      </c>
+      <c r="BC73">
+        <v>9</v>
+      </c>
+      <c r="BD73">
+        <v>1.26</v>
+      </c>
+      <c r="BE73">
+        <v>10.5</v>
+      </c>
+      <c r="BF73">
+        <v>4.15</v>
+      </c>
+      <c r="BG73">
+        <v>1.11</v>
+      </c>
+      <c r="BH73">
+        <v>5.5</v>
+      </c>
+      <c r="BI73">
+        <v>1.2</v>
+      </c>
+      <c r="BJ73">
+        <v>4.2</v>
+      </c>
+      <c r="BK73">
+        <v>1.36</v>
+      </c>
+      <c r="BL73">
+        <v>2.92</v>
+      </c>
+      <c r="BM73">
+        <v>1.61</v>
+      </c>
+      <c r="BN73">
+        <v>2.25</v>
+      </c>
+      <c r="BO73">
+        <v>1.91</v>
+      </c>
+      <c r="BP73">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -15078,22 +15078,22 @@
         <v>3.06</v>
       </c>
       <c r="AU69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW69">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX69">
         <v>3</v>
       </c>
       <c r="AY69">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AZ69">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA69">
         <v>9</v>
@@ -15287,19 +15287,19 @@
         <v>5</v>
       </c>
       <c r="AV70">
+        <v>9</v>
+      </c>
+      <c r="AW70">
         <v>8</v>
       </c>
-      <c r="AW70">
-        <v>4</v>
-      </c>
       <c r="AX70">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY70">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ70">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="BA70">
         <v>10</v>
@@ -15496,16 +15496,16 @@
         <v>7</v>
       </c>
       <c r="AW71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY71">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ71">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA71">
         <v>6</v>
@@ -15696,7 +15696,7 @@
         <v>4.08</v>
       </c>
       <c r="AU72">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AV72">
         <v>5</v>
@@ -15705,13 +15705,13 @@
         <v>5</v>
       </c>
       <c r="AX72">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY72">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ72">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA72">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="188">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -439,6 +439,12 @@
     <t>['90']</t>
   </si>
   <si>
+    <t>['45+3', '90+1']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -566,6 +572,12 @@
   </si>
   <si>
     <t>['25']</t>
+  </si>
+  <si>
+    <t>['10', '12', '70', '85', '72']</t>
+  </si>
+  <si>
+    <t>['70', '79', '86', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -927,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP73"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1389,7 +1401,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1595,7 +1607,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1673,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
         <v>0.43</v>
@@ -1801,7 +1813,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2291,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>0.43</v>
@@ -3037,7 +3049,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3118,7 +3130,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>1.39</v>
@@ -3321,7 +3333,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>0.86</v>
@@ -3449,7 +3461,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3530,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3655,7 +3667,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3861,7 +3873,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4067,7 +4079,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4273,7 +4285,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4479,7 +4491,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4891,7 +4903,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -4972,7 +4984,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR20">
         <v>0.64</v>
@@ -5097,7 +5109,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5175,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ21">
         <v>0.43</v>
@@ -5509,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5587,7 +5599,7 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>1.17</v>
@@ -5921,7 +5933,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6127,7 +6139,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6620,7 +6632,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ28">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -6951,7 +6963,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7157,7 +7169,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7569,7 +7581,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7775,7 +7787,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8059,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>0.67</v>
@@ -8187,7 +8199,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8265,10 +8277,10 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.74</v>
@@ -9011,7 +9023,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9217,7 +9229,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9295,7 +9307,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -9423,7 +9435,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9504,7 +9516,7 @@
         <v>2</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
         <v>2.48</v>
@@ -9629,7 +9641,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9835,7 +9847,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10325,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ46">
         <v>0.67</v>
@@ -10453,7 +10465,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10659,7 +10671,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10946,7 +10958,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ49">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.78</v>
@@ -11071,7 +11083,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11277,7 +11289,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11358,7 +11370,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR51">
         <v>1.5</v>
@@ -11483,7 +11495,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11689,7 +11701,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11895,7 +11907,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12101,7 +12113,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12179,7 +12191,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>0.43</v>
@@ -12591,7 +12603,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ57">
         <v>0.8</v>
@@ -12925,7 +12937,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13337,7 +13349,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13543,7 +13555,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13621,10 +13633,10 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -13955,7 +13967,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14036,7 +14048,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ64">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR64">
         <v>1.25</v>
@@ -14367,7 +14379,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14573,7 +14585,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14985,7 +14997,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15063,7 +15075,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ69">
         <v>1.33</v>
@@ -15191,7 +15203,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15397,7 +15409,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15603,7 +15615,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -15966,6 +15978,418 @@
       </c>
       <c r="BP73">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7796941</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45835.64583333334</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>72</v>
+      </c>
+      <c r="H74" t="s">
+        <v>71</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="M74">
+        <v>5</v>
+      </c>
+      <c r="N74">
+        <v>7</v>
+      </c>
+      <c r="O74" t="s">
+        <v>141</v>
+      </c>
+      <c r="P74" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q74">
+        <v>3.15</v>
+      </c>
+      <c r="R74">
+        <v>2.5</v>
+      </c>
+      <c r="S74">
+        <v>2.63</v>
+      </c>
+      <c r="T74">
+        <v>1.19</v>
+      </c>
+      <c r="U74">
+        <v>4.1</v>
+      </c>
+      <c r="V74">
+        <v>2.1</v>
+      </c>
+      <c r="W74">
+        <v>1.72</v>
+      </c>
+      <c r="X74">
+        <v>4.33</v>
+      </c>
+      <c r="Y74">
+        <v>1.17</v>
+      </c>
+      <c r="Z74">
+        <v>2.8</v>
+      </c>
+      <c r="AA74">
+        <v>3.5</v>
+      </c>
+      <c r="AB74">
+        <v>2.1</v>
+      </c>
+      <c r="AC74">
+        <v>1.02</v>
+      </c>
+      <c r="AD74">
+        <v>16.5</v>
+      </c>
+      <c r="AE74">
+        <v>1.14</v>
+      </c>
+      <c r="AF74">
+        <v>5.3</v>
+      </c>
+      <c r="AG74">
+        <v>1.45</v>
+      </c>
+      <c r="AH74">
+        <v>2.5</v>
+      </c>
+      <c r="AI74">
+        <v>1.38</v>
+      </c>
+      <c r="AJ74">
+        <v>2.7</v>
+      </c>
+      <c r="AK74">
+        <v>1.22</v>
+      </c>
+      <c r="AL74">
+        <v>1.25</v>
+      </c>
+      <c r="AM74">
+        <v>1.35</v>
+      </c>
+      <c r="AN74">
+        <v>1.33</v>
+      </c>
+      <c r="AO74">
+        <v>0.8</v>
+      </c>
+      <c r="AP74">
+        <v>1.14</v>
+      </c>
+      <c r="AQ74">
+        <v>1.17</v>
+      </c>
+      <c r="AR74">
+        <v>1.62</v>
+      </c>
+      <c r="AS74">
+        <v>1.48</v>
+      </c>
+      <c r="AT74">
+        <v>3.1</v>
+      </c>
+      <c r="AU74">
+        <v>5</v>
+      </c>
+      <c r="AV74">
+        <v>9</v>
+      </c>
+      <c r="AW74">
+        <v>3</v>
+      </c>
+      <c r="AX74">
+        <v>11</v>
+      </c>
+      <c r="AY74">
+        <v>8</v>
+      </c>
+      <c r="AZ74">
+        <v>20</v>
+      </c>
+      <c r="BA74">
+        <v>6</v>
+      </c>
+      <c r="BB74">
+        <v>6</v>
+      </c>
+      <c r="BC74">
+        <v>12</v>
+      </c>
+      <c r="BD74">
+        <v>1.94</v>
+      </c>
+      <c r="BE74">
+        <v>7.4</v>
+      </c>
+      <c r="BF74">
+        <v>2.26</v>
+      </c>
+      <c r="BG74">
+        <v>1.11</v>
+      </c>
+      <c r="BH74">
+        <v>5.5</v>
+      </c>
+      <c r="BI74">
+        <v>1.15</v>
+      </c>
+      <c r="BJ74">
+        <v>4.75</v>
+      </c>
+      <c r="BK74">
+        <v>1.29</v>
+      </c>
+      <c r="BL74">
+        <v>3.45</v>
+      </c>
+      <c r="BM74">
+        <v>1.48</v>
+      </c>
+      <c r="BN74">
+        <v>2.5</v>
+      </c>
+      <c r="BO74">
+        <v>1.78</v>
+      </c>
+      <c r="BP74">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7796940</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45835.67708333334</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <v>5</v>
+      </c>
+      <c r="O75" t="s">
+        <v>142</v>
+      </c>
+      <c r="P75" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q75">
+        <v>2.7</v>
+      </c>
+      <c r="R75">
+        <v>2.44</v>
+      </c>
+      <c r="S75">
+        <v>2.94</v>
+      </c>
+      <c r="T75">
+        <v>1.16</v>
+      </c>
+      <c r="U75">
+        <v>4.4</v>
+      </c>
+      <c r="V75">
+        <v>1.93</v>
+      </c>
+      <c r="W75">
+        <v>1.87</v>
+      </c>
+      <c r="X75">
+        <v>4</v>
+      </c>
+      <c r="Y75">
+        <v>1.2</v>
+      </c>
+      <c r="Z75">
+        <v>2.3</v>
+      </c>
+      <c r="AA75">
+        <v>3.9</v>
+      </c>
+      <c r="AB75">
+        <v>2.5</v>
+      </c>
+      <c r="AC75">
+        <v>1.01</v>
+      </c>
+      <c r="AD75">
+        <v>23</v>
+      </c>
+      <c r="AE75">
+        <v>1.08</v>
+      </c>
+      <c r="AF75">
+        <v>6.2</v>
+      </c>
+      <c r="AG75">
+        <v>1.35</v>
+      </c>
+      <c r="AH75">
+        <v>2.88</v>
+      </c>
+      <c r="AI75">
+        <v>1.34</v>
+      </c>
+      <c r="AJ75">
+        <v>2.9</v>
+      </c>
+      <c r="AK75">
+        <v>1.21</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>1.58</v>
+      </c>
+      <c r="AN75">
+        <v>2.29</v>
+      </c>
+      <c r="AO75">
+        <v>1.8</v>
+      </c>
+      <c r="AP75">
+        <v>2</v>
+      </c>
+      <c r="AQ75">
+        <v>2</v>
+      </c>
+      <c r="AR75">
+        <v>1.7</v>
+      </c>
+      <c r="AS75">
+        <v>1.5</v>
+      </c>
+      <c r="AT75">
+        <v>3.2</v>
+      </c>
+      <c r="AU75">
+        <v>5</v>
+      </c>
+      <c r="AV75">
+        <v>11</v>
+      </c>
+      <c r="AW75">
+        <v>6</v>
+      </c>
+      <c r="AX75">
+        <v>3</v>
+      </c>
+      <c r="AY75">
+        <v>11</v>
+      </c>
+      <c r="AZ75">
+        <v>14</v>
+      </c>
+      <c r="BA75">
+        <v>3</v>
+      </c>
+      <c r="BB75">
+        <v>2</v>
+      </c>
+      <c r="BC75">
+        <v>5</v>
+      </c>
+      <c r="BD75">
+        <v>2.44</v>
+      </c>
+      <c r="BE75">
+        <v>7.3</v>
+      </c>
+      <c r="BF75">
+        <v>1.69</v>
+      </c>
+      <c r="BG75">
+        <v>1.1</v>
+      </c>
+      <c r="BH75">
+        <v>5.75</v>
+      </c>
+      <c r="BI75">
+        <v>1.14</v>
+      </c>
+      <c r="BJ75">
+        <v>4.6</v>
+      </c>
+      <c r="BK75">
+        <v>1.32</v>
+      </c>
+      <c r="BL75">
+        <v>3.35</v>
+      </c>
+      <c r="BM75">
+        <v>1.5</v>
+      </c>
+      <c r="BN75">
+        <v>2.43</v>
+      </c>
+      <c r="BO75">
+        <v>1.83</v>
+      </c>
+      <c r="BP75">
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -16326,22 +16326,22 @@
         <v>3.2</v>
       </c>
       <c r="AU75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX75">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY75">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ75">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA75">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -16326,22 +16326,22 @@
         <v>3.2</v>
       </c>
       <c r="AU75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX75">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY75">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ75">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA75">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -16326,22 +16326,22 @@
         <v>3.2</v>
       </c>
       <c r="AU75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX75">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY75">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ75">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA75">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="194">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -445,6 +445,15 @@
     <t>['8']</t>
   </si>
   <si>
+    <t>['18', '29']</t>
+  </si>
+  <si>
+    <t>['51', '80']</t>
+  </si>
+  <si>
+    <t>['48', '66', '90+1']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -578,6 +587,15 @@
   </si>
   <si>
     <t>['70', '79', '86', '90+5']</t>
+  </si>
+  <si>
+    <t>['52', '66']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['28', '63']</t>
   </si>
 </sst>
 </file>
@@ -939,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1276,7 +1294,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1401,7 +1419,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1607,7 +1625,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1813,7 +1831,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -1891,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ5">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2100,7 +2118,7 @@
         <v>3</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2306,7 +2324,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2509,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ8">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2718,7 +2736,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ9">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3049,7 +3067,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3127,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11">
         <v>2</v>
@@ -3336,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>1.35</v>
@@ -3461,7 +3479,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3539,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ13">
         <v>1.17</v>
@@ -3667,7 +3685,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3873,7 +3891,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4079,7 +4097,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4285,7 +4303,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4491,7 +4509,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4903,7 +4921,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -4981,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ20">
         <v>2</v>
@@ -5109,7 +5127,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5190,7 +5208,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ21">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR21">
         <v>1.55</v>
@@ -5393,10 +5411,10 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ22">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR22">
         <v>1.24</v>
@@ -5521,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5602,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.37</v>
@@ -5805,10 +5823,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ24">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR24">
         <v>1.52</v>
@@ -5933,7 +5951,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6139,7 +6157,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6963,7 +6981,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7169,7 +7187,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7453,10 +7471,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR32">
         <v>0.75</v>
@@ -7581,7 +7599,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7659,10 +7677,10 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.71</v>
@@ -7787,7 +7805,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -7868,7 +7886,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ34">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>1.97</v>
@@ -8199,7 +8217,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8486,7 +8504,7 @@
         <v>3</v>
       </c>
       <c r="AQ37">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -8689,7 +8707,7 @@
         <v>2.33</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ38">
         <v>1.17</v>
@@ -9023,7 +9041,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9229,7 +9247,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9435,7 +9453,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9641,7 +9659,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9722,7 +9740,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ43">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -9847,7 +9865,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -9925,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -10134,7 +10152,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ45">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>2.3</v>
@@ -10340,7 +10358,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ46">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR46">
         <v>1.53</v>
@@ -10465,7 +10483,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10543,7 +10561,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ47">
         <v>0.8</v>
@@ -10671,7 +10689,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10752,7 +10770,7 @@
         <v>3</v>
       </c>
       <c r="AQ48">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR48">
         <v>1.76</v>
@@ -11083,7 +11101,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11161,7 +11179,7 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11289,7 +11307,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11495,7 +11513,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11576,7 +11594,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ52">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR52">
         <v>1.21</v>
@@ -11701,7 +11719,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11779,7 +11797,7 @@
         <v>0.25</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ53">
         <v>0.67</v>
@@ -11907,7 +11925,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -11988,7 +12006,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR54">
         <v>2.31</v>
@@ -12113,7 +12131,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12397,7 +12415,7 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ56">
         <v>1.17</v>
@@ -12812,7 +12830,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ58">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -12937,7 +12955,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13018,7 +13036,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ59">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13349,7 +13367,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13555,7 +13573,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13839,7 +13857,7 @@
         <v>0.8</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ63">
         <v>0.67</v>
@@ -13967,7 +13985,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14251,10 +14269,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ65">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR65">
         <v>1.59</v>
@@ -14379,7 +14397,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14460,7 +14478,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR66">
         <v>1.5</v>
@@ -14585,7 +14603,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14997,7 +15015,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15203,7 +15221,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15409,7 +15427,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15490,7 +15508,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ71">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR71">
         <v>1.16</v>
@@ -15615,7 +15633,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16027,7 +16045,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16233,7 +16251,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16390,6 +16408,830 @@
       </c>
       <c r="BP75">
         <v>1.87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7796942</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45837.58333333334</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" t="s">
+        <v>81</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
+      </c>
+      <c r="L76">
+        <v>2</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76" t="s">
+        <v>143</v>
+      </c>
+      <c r="P76" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q76">
+        <v>2.9</v>
+      </c>
+      <c r="R76">
+        <v>2.25</v>
+      </c>
+      <c r="S76">
+        <v>3.27</v>
+      </c>
+      <c r="T76">
+        <v>1.29</v>
+      </c>
+      <c r="U76">
+        <v>3.4</v>
+      </c>
+      <c r="V76">
+        <v>2.25</v>
+      </c>
+      <c r="W76">
+        <v>1.63</v>
+      </c>
+      <c r="X76">
+        <v>4.8</v>
+      </c>
+      <c r="Y76">
+        <v>1.13</v>
+      </c>
+      <c r="Z76">
+        <v>2.2</v>
+      </c>
+      <c r="AA76">
+        <v>3.4</v>
+      </c>
+      <c r="AB76">
+        <v>2.62</v>
+      </c>
+      <c r="AC76">
+        <v>1.03</v>
+      </c>
+      <c r="AD76">
+        <v>17</v>
+      </c>
+      <c r="AE76">
+        <v>1.1</v>
+      </c>
+      <c r="AF76">
+        <v>5</v>
+      </c>
+      <c r="AG76">
+        <v>1.57</v>
+      </c>
+      <c r="AH76">
+        <v>2.35</v>
+      </c>
+      <c r="AI76">
+        <v>1.5</v>
+      </c>
+      <c r="AJ76">
+        <v>2.5</v>
+      </c>
+      <c r="AK76">
+        <v>1.29</v>
+      </c>
+      <c r="AL76">
+        <v>1.25</v>
+      </c>
+      <c r="AM76">
+        <v>1.57</v>
+      </c>
+      <c r="AN76">
+        <v>2</v>
+      </c>
+      <c r="AO76">
+        <v>1.17</v>
+      </c>
+      <c r="AP76">
+        <v>2.14</v>
+      </c>
+      <c r="AQ76">
+        <v>1</v>
+      </c>
+      <c r="AR76">
+        <v>1.62</v>
+      </c>
+      <c r="AS76">
+        <v>1.5</v>
+      </c>
+      <c r="AT76">
+        <v>3.12</v>
+      </c>
+      <c r="AU76">
+        <v>8</v>
+      </c>
+      <c r="AV76">
+        <v>5</v>
+      </c>
+      <c r="AW76">
+        <v>4</v>
+      </c>
+      <c r="AX76">
+        <v>5</v>
+      </c>
+      <c r="AY76">
+        <v>12</v>
+      </c>
+      <c r="AZ76">
+        <v>10</v>
+      </c>
+      <c r="BA76">
+        <v>4</v>
+      </c>
+      <c r="BB76">
+        <v>3</v>
+      </c>
+      <c r="BC76">
+        <v>7</v>
+      </c>
+      <c r="BD76">
+        <v>1.72</v>
+      </c>
+      <c r="BE76">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF76">
+        <v>2.57</v>
+      </c>
+      <c r="BG76">
+        <v>1.12</v>
+      </c>
+      <c r="BH76">
+        <v>5.45</v>
+      </c>
+      <c r="BI76">
+        <v>1.18</v>
+      </c>
+      <c r="BJ76">
+        <v>3.94</v>
+      </c>
+      <c r="BK76">
+        <v>1.4</v>
+      </c>
+      <c r="BL76">
+        <v>2.8</v>
+      </c>
+      <c r="BM76">
+        <v>1.63</v>
+      </c>
+      <c r="BN76">
+        <v>2.1</v>
+      </c>
+      <c r="BO76">
+        <v>2</v>
+      </c>
+      <c r="BP76">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7796943</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45837.58333333334</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s">
+        <v>79</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>2</v>
+      </c>
+      <c r="O77" t="s">
+        <v>85</v>
+      </c>
+      <c r="P77" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q77">
+        <v>2.4</v>
+      </c>
+      <c r="R77">
+        <v>2.25</v>
+      </c>
+      <c r="S77">
+        <v>4</v>
+      </c>
+      <c r="T77">
+        <v>1.27</v>
+      </c>
+      <c r="U77">
+        <v>3.28</v>
+      </c>
+      <c r="V77">
+        <v>2.39</v>
+      </c>
+      <c r="W77">
+        <v>1.55</v>
+      </c>
+      <c r="X77">
+        <v>5</v>
+      </c>
+      <c r="Y77">
+        <v>1.12</v>
+      </c>
+      <c r="Z77">
+        <v>1.97</v>
+      </c>
+      <c r="AA77">
+        <v>3.4</v>
+      </c>
+      <c r="AB77">
+        <v>3.2</v>
+      </c>
+      <c r="AC77">
+        <v>1.03</v>
+      </c>
+      <c r="AD77">
+        <v>13</v>
+      </c>
+      <c r="AE77">
+        <v>1.15</v>
+      </c>
+      <c r="AF77">
+        <v>4.3</v>
+      </c>
+      <c r="AG77">
+        <v>1.61</v>
+      </c>
+      <c r="AH77">
+        <v>2.25</v>
+      </c>
+      <c r="AI77">
+        <v>1.53</v>
+      </c>
+      <c r="AJ77">
+        <v>2.34</v>
+      </c>
+      <c r="AK77">
+        <v>1.29</v>
+      </c>
+      <c r="AL77">
+        <v>1.27</v>
+      </c>
+      <c r="AM77">
+        <v>1.82</v>
+      </c>
+      <c r="AN77">
+        <v>2</v>
+      </c>
+      <c r="AO77">
+        <v>0.86</v>
+      </c>
+      <c r="AP77">
+        <v>1.71</v>
+      </c>
+      <c r="AQ77">
+        <v>1.13</v>
+      </c>
+      <c r="AR77">
+        <v>0.98</v>
+      </c>
+      <c r="AS77">
+        <v>1.67</v>
+      </c>
+      <c r="AT77">
+        <v>2.65</v>
+      </c>
+      <c r="AU77">
+        <v>3</v>
+      </c>
+      <c r="AV77">
+        <v>5</v>
+      </c>
+      <c r="AW77">
+        <v>8</v>
+      </c>
+      <c r="AX77">
+        <v>7</v>
+      </c>
+      <c r="AY77">
+        <v>11</v>
+      </c>
+      <c r="AZ77">
+        <v>12</v>
+      </c>
+      <c r="BA77">
+        <v>7</v>
+      </c>
+      <c r="BB77">
+        <v>5</v>
+      </c>
+      <c r="BC77">
+        <v>12</v>
+      </c>
+      <c r="BD77">
+        <v>1.82</v>
+      </c>
+      <c r="BE77">
+        <v>7.4</v>
+      </c>
+      <c r="BF77">
+        <v>2.47</v>
+      </c>
+      <c r="BG77">
+        <v>1.15</v>
+      </c>
+      <c r="BH77">
+        <v>4.75</v>
+      </c>
+      <c r="BI77">
+        <v>1.22</v>
+      </c>
+      <c r="BJ77">
+        <v>3.3</v>
+      </c>
+      <c r="BK77">
+        <v>1.56</v>
+      </c>
+      <c r="BL77">
+        <v>2.4</v>
+      </c>
+      <c r="BM77">
+        <v>1.75</v>
+      </c>
+      <c r="BN77">
+        <v>1.94</v>
+      </c>
+      <c r="BO77">
+        <v>2.05</v>
+      </c>
+      <c r="BP77">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7796944</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45837.67708333334</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" t="s">
+        <v>77</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>3</v>
+      </c>
+      <c r="O78" t="s">
+        <v>144</v>
+      </c>
+      <c r="P78" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q78">
+        <v>1.71</v>
+      </c>
+      <c r="R78">
+        <v>2.8</v>
+      </c>
+      <c r="S78">
+        <v>5.75</v>
+      </c>
+      <c r="T78">
+        <v>1.2</v>
+      </c>
+      <c r="U78">
+        <v>4.1</v>
+      </c>
+      <c r="V78">
+        <v>2.09</v>
+      </c>
+      <c r="W78">
+        <v>1.75</v>
+      </c>
+      <c r="X78">
+        <v>3.9</v>
+      </c>
+      <c r="Y78">
+        <v>1.16</v>
+      </c>
+      <c r="Z78">
+        <v>1.33</v>
+      </c>
+      <c r="AA78">
+        <v>5.45</v>
+      </c>
+      <c r="AB78">
+        <v>6.8</v>
+      </c>
+      <c r="AC78">
+        <v>1.01</v>
+      </c>
+      <c r="AD78">
+        <v>17.5</v>
+      </c>
+      <c r="AE78">
+        <v>1.07</v>
+      </c>
+      <c r="AF78">
+        <v>5.85</v>
+      </c>
+      <c r="AG78">
+        <v>1.36</v>
+      </c>
+      <c r="AH78">
+        <v>2.75</v>
+      </c>
+      <c r="AI78">
+        <v>1.64</v>
+      </c>
+      <c r="AJ78">
+        <v>2.1</v>
+      </c>
+      <c r="AK78">
+        <v>1.09</v>
+      </c>
+      <c r="AL78">
+        <v>1.13</v>
+      </c>
+      <c r="AM78">
+        <v>3.25</v>
+      </c>
+      <c r="AN78">
+        <v>3</v>
+      </c>
+      <c r="AO78">
+        <v>0.67</v>
+      </c>
+      <c r="AP78">
+        <v>3</v>
+      </c>
+      <c r="AQ78">
+        <v>0.57</v>
+      </c>
+      <c r="AR78">
+        <v>1.66</v>
+      </c>
+      <c r="AS78">
+        <v>1.44</v>
+      </c>
+      <c r="AT78">
+        <v>3.1</v>
+      </c>
+      <c r="AU78">
+        <v>5</v>
+      </c>
+      <c r="AV78">
+        <v>5</v>
+      </c>
+      <c r="AW78">
+        <v>3</v>
+      </c>
+      <c r="AX78">
+        <v>7</v>
+      </c>
+      <c r="AY78">
+        <v>8</v>
+      </c>
+      <c r="AZ78">
+        <v>12</v>
+      </c>
+      <c r="BA78">
+        <v>4</v>
+      </c>
+      <c r="BB78">
+        <v>7</v>
+      </c>
+      <c r="BC78">
+        <v>11</v>
+      </c>
+      <c r="BD78">
+        <v>1.27</v>
+      </c>
+      <c r="BE78">
+        <v>12.5</v>
+      </c>
+      <c r="BF78">
+        <v>4.2</v>
+      </c>
+      <c r="BG78">
+        <v>1.12</v>
+      </c>
+      <c r="BH78">
+        <v>5.45</v>
+      </c>
+      <c r="BI78">
+        <v>1.18</v>
+      </c>
+      <c r="BJ78">
+        <v>3.6</v>
+      </c>
+      <c r="BK78">
+        <v>1.35</v>
+      </c>
+      <c r="BL78">
+        <v>2.7</v>
+      </c>
+      <c r="BM78">
+        <v>1.63</v>
+      </c>
+      <c r="BN78">
+        <v>2.19</v>
+      </c>
+      <c r="BO78">
+        <v>2.02</v>
+      </c>
+      <c r="BP78">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7796945</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45837.67708333334</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s">
+        <v>80</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>3</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>5</v>
+      </c>
+      <c r="O79" t="s">
+        <v>145</v>
+      </c>
+      <c r="P79" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q79">
+        <v>2.4</v>
+      </c>
+      <c r="R79">
+        <v>2.84</v>
+      </c>
+      <c r="S79">
+        <v>3</v>
+      </c>
+      <c r="T79">
+        <v>1.17</v>
+      </c>
+      <c r="U79">
+        <v>4.6</v>
+      </c>
+      <c r="V79">
+        <v>1.84</v>
+      </c>
+      <c r="W79">
+        <v>1.93</v>
+      </c>
+      <c r="X79">
+        <v>3.85</v>
+      </c>
+      <c r="Y79">
+        <v>1.25</v>
+      </c>
+      <c r="Z79">
+        <v>2.25</v>
+      </c>
+      <c r="AA79">
+        <v>3.8</v>
+      </c>
+      <c r="AB79">
+        <v>2.65</v>
+      </c>
+      <c r="AC79">
+        <v>1</v>
+      </c>
+      <c r="AD79">
+        <v>21</v>
+      </c>
+      <c r="AE79">
+        <v>1.06</v>
+      </c>
+      <c r="AF79">
+        <v>7.75</v>
+      </c>
+      <c r="AG79">
+        <v>1.24</v>
+      </c>
+      <c r="AH79">
+        <v>3.4</v>
+      </c>
+      <c r="AI79">
+        <v>1.27</v>
+      </c>
+      <c r="AJ79">
+        <v>3.3</v>
+      </c>
+      <c r="AK79">
+        <v>1.41</v>
+      </c>
+      <c r="AL79">
+        <v>1.23</v>
+      </c>
+      <c r="AM79">
+        <v>1.7</v>
+      </c>
+      <c r="AN79">
+        <v>2</v>
+      </c>
+      <c r="AO79">
+        <v>0.43</v>
+      </c>
+      <c r="AP79">
+        <v>2.17</v>
+      </c>
+      <c r="AQ79">
+        <v>0.38</v>
+      </c>
+      <c r="AR79">
+        <v>1.87</v>
+      </c>
+      <c r="AS79">
+        <v>1.57</v>
+      </c>
+      <c r="AT79">
+        <v>3.44</v>
+      </c>
+      <c r="AU79">
+        <v>5</v>
+      </c>
+      <c r="AV79">
+        <v>5</v>
+      </c>
+      <c r="AW79">
+        <v>15</v>
+      </c>
+      <c r="AX79">
+        <v>1</v>
+      </c>
+      <c r="AY79">
+        <v>20</v>
+      </c>
+      <c r="AZ79">
+        <v>6</v>
+      </c>
+      <c r="BA79">
+        <v>10</v>
+      </c>
+      <c r="BB79">
+        <v>1</v>
+      </c>
+      <c r="BC79">
+        <v>11</v>
+      </c>
+      <c r="BD79">
+        <v>1.57</v>
+      </c>
+      <c r="BE79">
+        <v>7.6</v>
+      </c>
+      <c r="BF79">
+        <v>3.14</v>
+      </c>
+      <c r="BG79">
+        <v>0</v>
+      </c>
+      <c r="BH79">
+        <v>0</v>
+      </c>
+      <c r="BI79">
+        <v>1.15</v>
+      </c>
+      <c r="BJ79">
+        <v>4.5</v>
+      </c>
+      <c r="BK79">
+        <v>1.23</v>
+      </c>
+      <c r="BL79">
+        <v>3.42</v>
+      </c>
+      <c r="BM79">
+        <v>1.43</v>
+      </c>
+      <c r="BN79">
+        <v>2.26</v>
+      </c>
+      <c r="BO79">
+        <v>1.8</v>
+      </c>
+      <c r="BP79">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -16553,19 +16553,19 @@
         <v>8</v>
       </c>
       <c r="AV76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW76">
         <v>4</v>
       </c>
       <c r="AX76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY76">
         <v>12</v>
       </c>
       <c r="AZ76">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA76">
         <v>4</v>
@@ -16756,22 +16756,22 @@
         <v>2.65</v>
       </c>
       <c r="AU77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW77">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX77">
         <v>7</v>
       </c>
       <c r="AY77">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ77">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA77">
         <v>7</v>
@@ -16965,19 +16965,19 @@
         <v>5</v>
       </c>
       <c r="AV78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX78">
+        <v>9</v>
+      </c>
+      <c r="AY78">
         <v>7</v>
       </c>
-      <c r="AY78">
-        <v>8</v>
-      </c>
       <c r="AZ78">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA78">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -451,7 +451,7 @@
     <t>['51', '80']</t>
   </si>
   <si>
-    <t>['48', '66', '90+1']</t>
+    <t>['66', '90+1', '47']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -595,7 +595,7 @@
     <t>['53']</t>
   </si>
   <si>
-    <t>['28', '63']</t>
+    <t>['63', '27']</t>
   </si>
 </sst>
 </file>
@@ -16553,19 +16553,19 @@
         <v>8</v>
       </c>
       <c r="AV76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW76">
         <v>4</v>
       </c>
       <c r="AX76">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY76">
         <v>12</v>
       </c>
       <c r="AZ76">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA76">
         <v>4</v>
@@ -16756,22 +16756,22 @@
         <v>2.65</v>
       </c>
       <c r="AU77">
+        <v>3</v>
+      </c>
+      <c r="AV77">
         <v>5</v>
       </c>
-      <c r="AV77">
+      <c r="AW77">
         <v>7</v>
       </c>
-      <c r="AW77">
+      <c r="AX77">
+        <v>4</v>
+      </c>
+      <c r="AY77">
+        <v>10</v>
+      </c>
+      <c r="AZ77">
         <v>9</v>
-      </c>
-      <c r="AX77">
-        <v>7</v>
-      </c>
-      <c r="AY77">
-        <v>14</v>
-      </c>
-      <c r="AZ77">
-        <v>14</v>
       </c>
       <c r="BA77">
         <v>7</v>
@@ -16965,19 +16965,19 @@
         <v>5</v>
       </c>
       <c r="AV78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX78">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY78">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ78">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA78">
         <v>4</v>
@@ -17174,13 +17174,13 @@
         <v>5</v>
       </c>
       <c r="AW79">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX79">
         <v>1</v>
       </c>
       <c r="AY79">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ79">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -16553,19 +16553,19 @@
         <v>8</v>
       </c>
       <c r="AV76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW76">
         <v>4</v>
       </c>
       <c r="AX76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY76">
         <v>12</v>
       </c>
       <c r="AZ76">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA76">
         <v>4</v>
@@ -16756,22 +16756,22 @@
         <v>2.65</v>
       </c>
       <c r="AU77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW77">
+        <v>9</v>
+      </c>
+      <c r="AX77">
         <v>7</v>
       </c>
-      <c r="AX77">
-        <v>4</v>
-      </c>
       <c r="AY77">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ77">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA77">
         <v>7</v>
@@ -16965,19 +16965,19 @@
         <v>5</v>
       </c>
       <c r="AV78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX78">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ78">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA78">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="196">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -454,6 +454,9 @@
     <t>['66', '90+1', '47']</t>
   </si>
   <si>
+    <t>['44', '47']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -596,6 +599,9 @@
   </si>
   <si>
     <t>['63', '27']</t>
+  </si>
+  <si>
+    <t>['7', '37']</t>
   </si>
 </sst>
 </file>
@@ -957,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP79"/>
+  <dimension ref="A1:BP80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1419,7 +1425,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1625,7 +1631,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1831,7 +1837,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2733,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3067,7 +3073,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3148,7 +3154,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR11">
         <v>1.39</v>
@@ -3479,7 +3485,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3685,7 +3691,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3891,7 +3897,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4097,7 +4103,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4303,7 +4309,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4509,7 +4515,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4793,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -4921,7 +4927,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5002,7 +5008,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ20">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR20">
         <v>0.64</v>
@@ -5127,7 +5133,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5539,7 +5545,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5951,7 +5957,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6157,7 +6163,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6853,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>0.8</v>
@@ -6981,7 +6987,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7187,7 +7193,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7599,7 +7605,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7805,7 +7811,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8217,7 +8223,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8298,7 +8304,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR36">
         <v>1.74</v>
@@ -9041,7 +9047,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9119,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>0.43</v>
@@ -9247,7 +9253,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9453,7 +9459,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9659,7 +9665,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9865,7 +9871,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10483,7 +10489,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10689,7 +10695,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10976,7 +10982,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR49">
         <v>1.78</v>
@@ -11101,7 +11107,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11307,7 +11313,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11385,7 +11391,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>1.17</v>
@@ -11513,7 +11519,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11719,7 +11725,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11925,7 +11931,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12131,7 +12137,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12955,7 +12961,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13367,7 +13373,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13573,7 +13579,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13985,7 +13991,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14066,7 +14072,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ64">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR64">
         <v>1.25</v>
@@ -14397,7 +14403,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14475,7 +14481,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>1.13</v>
@@ -14603,7 +14609,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -15015,7 +15021,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15221,7 +15227,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15427,7 +15433,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15633,7 +15639,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16045,7 +16051,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16251,7 +16257,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16332,7 +16338,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR75">
         <v>1.7</v>
@@ -16663,7 +16669,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16869,7 +16875,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17075,7 +17081,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17232,6 +17238,212 @@
       </c>
       <c r="BP79">
         <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7796946</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45841.67708333334</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>77</v>
+      </c>
+      <c r="H80" t="s">
+        <v>70</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>3</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80">
+        <v>4</v>
+      </c>
+      <c r="O80" t="s">
+        <v>146</v>
+      </c>
+      <c r="P80" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q80">
+        <v>3.9</v>
+      </c>
+      <c r="R80">
+        <v>2.37</v>
+      </c>
+      <c r="S80">
+        <v>2.26</v>
+      </c>
+      <c r="T80">
+        <v>1.25</v>
+      </c>
+      <c r="U80">
+        <v>3.5</v>
+      </c>
+      <c r="V80">
+        <v>2.26</v>
+      </c>
+      <c r="W80">
+        <v>1.65</v>
+      </c>
+      <c r="X80">
+        <v>4.6</v>
+      </c>
+      <c r="Y80">
+        <v>1.15</v>
+      </c>
+      <c r="Z80">
+        <v>3.97</v>
+      </c>
+      <c r="AA80">
+        <v>4.1</v>
+      </c>
+      <c r="AB80">
+        <v>1.71</v>
+      </c>
+      <c r="AC80">
+        <v>1.03</v>
+      </c>
+      <c r="AD80">
+        <v>12</v>
+      </c>
+      <c r="AE80">
+        <v>1.17</v>
+      </c>
+      <c r="AF80">
+        <v>5</v>
+      </c>
+      <c r="AG80">
+        <v>1.53</v>
+      </c>
+      <c r="AH80">
+        <v>2.37</v>
+      </c>
+      <c r="AI80">
+        <v>1.53</v>
+      </c>
+      <c r="AJ80">
+        <v>2.4</v>
+      </c>
+      <c r="AK80">
+        <v>1.22</v>
+      </c>
+      <c r="AL80">
+        <v>1.18</v>
+      </c>
+      <c r="AM80">
+        <v>1.2</v>
+      </c>
+      <c r="AN80">
+        <v>2.17</v>
+      </c>
+      <c r="AO80">
+        <v>2</v>
+      </c>
+      <c r="AP80">
+        <v>2</v>
+      </c>
+      <c r="AQ80">
+        <v>1.86</v>
+      </c>
+      <c r="AR80">
+        <v>1.57</v>
+      </c>
+      <c r="AS80">
+        <v>1.66</v>
+      </c>
+      <c r="AT80">
+        <v>3.23</v>
+      </c>
+      <c r="AU80">
+        <v>7</v>
+      </c>
+      <c r="AV80">
+        <v>4</v>
+      </c>
+      <c r="AW80">
+        <v>7</v>
+      </c>
+      <c r="AX80">
+        <v>12</v>
+      </c>
+      <c r="AY80">
+        <v>14</v>
+      </c>
+      <c r="AZ80">
+        <v>16</v>
+      </c>
+      <c r="BA80">
+        <v>7</v>
+      </c>
+      <c r="BB80">
+        <v>10</v>
+      </c>
+      <c r="BC80">
+        <v>17</v>
+      </c>
+      <c r="BD80">
+        <v>3.62</v>
+      </c>
+      <c r="BE80">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF80">
+        <v>1.52</v>
+      </c>
+      <c r="BG80">
+        <v>1.1</v>
+      </c>
+      <c r="BH80">
+        <v>5.75</v>
+      </c>
+      <c r="BI80">
+        <v>1.2</v>
+      </c>
+      <c r="BJ80">
+        <v>4</v>
+      </c>
+      <c r="BK80">
+        <v>1.36</v>
+      </c>
+      <c r="BL80">
+        <v>2.9</v>
+      </c>
+      <c r="BM80">
+        <v>1.57</v>
+      </c>
+      <c r="BN80">
+        <v>2.25</v>
+      </c>
+      <c r="BO80">
+        <v>1.91</v>
+      </c>
+      <c r="BP80">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -17380,31 +17380,31 @@
         <v>3.23</v>
       </c>
       <c r="AU80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV80">
         <v>4</v>
       </c>
       <c r="AW80">
+        <v>2</v>
+      </c>
+      <c r="AX80">
+        <v>3</v>
+      </c>
+      <c r="AY80">
+        <v>10</v>
+      </c>
+      <c r="AZ80">
         <v>7</v>
-      </c>
-      <c r="AX80">
-        <v>12</v>
-      </c>
-      <c r="AY80">
-        <v>14</v>
-      </c>
-      <c r="AZ80">
-        <v>16</v>
       </c>
       <c r="BA80">
         <v>7</v>
       </c>
       <c r="BB80">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC80">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD80">
         <v>3.62</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -17380,31 +17380,31 @@
         <v>3.23</v>
       </c>
       <c r="AU80">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV80">
         <v>4</v>
       </c>
       <c r="AW80">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX80">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AY80">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ80">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA80">
         <v>7</v>
       </c>
       <c r="BB80">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD80">
         <v>3.62</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="197">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>['7', '37']</t>
+  </si>
+  <si>
+    <t>['18', '77']</t>
   </si>
 </sst>
 </file>
@@ -963,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP80"/>
+  <dimension ref="A1:BP82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2533,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>0.38</v>
@@ -3566,7 +3569,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ13">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3975,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15">
         <v>1.17</v>
@@ -4596,7 +4599,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ18">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5005,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1.86</v>
@@ -6447,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ27">
         <v>0.67</v>
@@ -6656,7 +6659,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -7274,7 +7277,7 @@
         <v>3</v>
       </c>
       <c r="AQ31">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>2.21</v>
@@ -7477,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>0.57</v>
@@ -8098,7 +8101,7 @@
         <v>2</v>
       </c>
       <c r="AQ35">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.56</v>
@@ -9540,7 +9543,7 @@
         <v>2</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR42">
         <v>2.48</v>
@@ -9743,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43">
         <v>0.38</v>
@@ -9952,7 +9955,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.64</v>
@@ -10567,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>0.8</v>
@@ -11185,7 +11188,7 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11394,7 +11397,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR51">
         <v>1.5</v>
@@ -13039,7 +13042,7 @@
         <v>0.8</v>
       </c>
       <c r="AP59">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13454,7 +13457,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ61">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>2.25</v>
@@ -13660,7 +13663,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -13863,7 +13866,7 @@
         <v>0.8</v>
       </c>
       <c r="AP63">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>0.67</v>
@@ -15305,7 +15308,7 @@
         <v>0.25</v>
       </c>
       <c r="AP70">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
         <v>0.8</v>
@@ -15926,7 +15929,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>2.14</v>
@@ -16132,7 +16135,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ74">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16747,7 +16750,7 @@
         <v>0.86</v>
       </c>
       <c r="AP77">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ77">
         <v>1.13</v>
@@ -17444,6 +17447,418 @@
       </c>
       <c r="BP80">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7796947</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45843.45833333334</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>76</v>
+      </c>
+      <c r="H81" t="s">
+        <v>71</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>2</v>
+      </c>
+      <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81" t="s">
+        <v>85</v>
+      </c>
+      <c r="P81" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q81">
+        <v>4.45</v>
+      </c>
+      <c r="R81">
+        <v>2.41</v>
+      </c>
+      <c r="S81">
+        <v>2.15</v>
+      </c>
+      <c r="T81">
+        <v>1.25</v>
+      </c>
+      <c r="U81">
+        <v>3.5</v>
+      </c>
+      <c r="V81">
+        <v>2.33</v>
+      </c>
+      <c r="W81">
+        <v>1.55</v>
+      </c>
+      <c r="X81">
+        <v>5.2</v>
+      </c>
+      <c r="Y81">
+        <v>1.15</v>
+      </c>
+      <c r="Z81">
+        <v>4.75</v>
+      </c>
+      <c r="AA81">
+        <v>4.1</v>
+      </c>
+      <c r="AB81">
+        <v>1.55</v>
+      </c>
+      <c r="AC81">
+        <v>1.02</v>
+      </c>
+      <c r="AD81">
+        <v>10</v>
+      </c>
+      <c r="AE81">
+        <v>1.15</v>
+      </c>
+      <c r="AF81">
+        <v>4.75</v>
+      </c>
+      <c r="AG81">
+        <v>1.53</v>
+      </c>
+      <c r="AH81">
+        <v>2.34</v>
+      </c>
+      <c r="AI81">
+        <v>1.57</v>
+      </c>
+      <c r="AJ81">
+        <v>2.25</v>
+      </c>
+      <c r="AK81">
+        <v>2.1</v>
+      </c>
+      <c r="AL81">
+        <v>1.2</v>
+      </c>
+      <c r="AM81">
+        <v>1.22</v>
+      </c>
+      <c r="AN81">
+        <v>1.71</v>
+      </c>
+      <c r="AO81">
+        <v>1.17</v>
+      </c>
+      <c r="AP81">
+        <v>1.5</v>
+      </c>
+      <c r="AQ81">
+        <v>1.43</v>
+      </c>
+      <c r="AR81">
+        <v>1.09</v>
+      </c>
+      <c r="AS81">
+        <v>1.62</v>
+      </c>
+      <c r="AT81">
+        <v>2.71</v>
+      </c>
+      <c r="AU81">
+        <v>0</v>
+      </c>
+      <c r="AV81">
+        <v>4</v>
+      </c>
+      <c r="AW81">
+        <v>0</v>
+      </c>
+      <c r="AX81">
+        <v>1</v>
+      </c>
+      <c r="AY81">
+        <v>0</v>
+      </c>
+      <c r="AZ81">
+        <v>5</v>
+      </c>
+      <c r="BA81">
+        <v>3</v>
+      </c>
+      <c r="BB81">
+        <v>4</v>
+      </c>
+      <c r="BC81">
+        <v>7</v>
+      </c>
+      <c r="BD81">
+        <v>3.28</v>
+      </c>
+      <c r="BE81">
+        <v>9.9</v>
+      </c>
+      <c r="BF81">
+        <v>1.28</v>
+      </c>
+      <c r="BG81">
+        <v>1.11</v>
+      </c>
+      <c r="BH81">
+        <v>5.5</v>
+      </c>
+      <c r="BI81">
+        <v>1.16</v>
+      </c>
+      <c r="BJ81">
+        <v>3.8</v>
+      </c>
+      <c r="BK81">
+        <v>1.38</v>
+      </c>
+      <c r="BL81">
+        <v>2.8</v>
+      </c>
+      <c r="BM81">
+        <v>1.62</v>
+      </c>
+      <c r="BN81">
+        <v>2.2</v>
+      </c>
+      <c r="BO81">
+        <v>1.95</v>
+      </c>
+      <c r="BP81">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7796948</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45843.45833333334</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s">
+        <v>73</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="s">
+        <v>85</v>
+      </c>
+      <c r="P82" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q82">
+        <v>3.28</v>
+      </c>
+      <c r="R82">
+        <v>2.37</v>
+      </c>
+      <c r="S82">
+        <v>2.65</v>
+      </c>
+      <c r="T82">
+        <v>1.25</v>
+      </c>
+      <c r="U82">
+        <v>3.7</v>
+      </c>
+      <c r="V82">
+        <v>2.1</v>
+      </c>
+      <c r="W82">
+        <v>1.68</v>
+      </c>
+      <c r="X82">
+        <v>4.4</v>
+      </c>
+      <c r="Y82">
+        <v>1.16</v>
+      </c>
+      <c r="Z82">
+        <v>2.64</v>
+      </c>
+      <c r="AA82">
+        <v>3.68</v>
+      </c>
+      <c r="AB82">
+        <v>2.23</v>
+      </c>
+      <c r="AC82">
+        <v>1.01</v>
+      </c>
+      <c r="AD82">
+        <v>17</v>
+      </c>
+      <c r="AE82">
+        <v>1.15</v>
+      </c>
+      <c r="AF82">
+        <v>5.65</v>
+      </c>
+      <c r="AG82">
+        <v>1.43</v>
+      </c>
+      <c r="AH82">
+        <v>2.62</v>
+      </c>
+      <c r="AI82">
+        <v>1.4</v>
+      </c>
+      <c r="AJ82">
+        <v>2.75</v>
+      </c>
+      <c r="AK82">
+        <v>1.22</v>
+      </c>
+      <c r="AL82">
+        <v>1.25</v>
+      </c>
+      <c r="AM82">
+        <v>1.45</v>
+      </c>
+      <c r="AN82">
+        <v>0.6</v>
+      </c>
+      <c r="AO82">
+        <v>0.67</v>
+      </c>
+      <c r="AP82">
+        <v>0.5</v>
+      </c>
+      <c r="AQ82">
+        <v>1</v>
+      </c>
+      <c r="AR82">
+        <v>1.59</v>
+      </c>
+      <c r="AS82">
+        <v>1.34</v>
+      </c>
+      <c r="AT82">
+        <v>2.93</v>
+      </c>
+      <c r="AU82">
+        <v>6</v>
+      </c>
+      <c r="AV82">
+        <v>4</v>
+      </c>
+      <c r="AW82">
+        <v>12</v>
+      </c>
+      <c r="AX82">
+        <v>8</v>
+      </c>
+      <c r="AY82">
+        <v>18</v>
+      </c>
+      <c r="AZ82">
+        <v>12</v>
+      </c>
+      <c r="BA82">
+        <v>6</v>
+      </c>
+      <c r="BB82">
+        <v>10</v>
+      </c>
+      <c r="BC82">
+        <v>16</v>
+      </c>
+      <c r="BD82">
+        <v>2.18</v>
+      </c>
+      <c r="BE82">
+        <v>6.8</v>
+      </c>
+      <c r="BF82">
+        <v>2</v>
+      </c>
+      <c r="BG82">
+        <v>1.03</v>
+      </c>
+      <c r="BH82">
+        <v>5.25</v>
+      </c>
+      <c r="BI82">
+        <v>1.15</v>
+      </c>
+      <c r="BJ82">
+        <v>3.6</v>
+      </c>
+      <c r="BK82">
+        <v>1.4</v>
+      </c>
+      <c r="BL82">
+        <v>2.7</v>
+      </c>
+      <c r="BM82">
+        <v>1.65</v>
+      </c>
+      <c r="BN82">
+        <v>2.1</v>
+      </c>
+      <c r="BO82">
+        <v>2</v>
+      </c>
+      <c r="BP82">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="197">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -966,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP82"/>
+  <dimension ref="A1:BP83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -4805,7 +4805,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR19">
         <v>1.5</v>
@@ -6041,7 +6041,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>2.26</v>
@@ -6244,7 +6244,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
         <v>1.17</v>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ39">
         <v>0.67</v>
@@ -9337,7 +9337,7 @@
         <v>2</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR41">
         <v>1.56</v>
@@ -11191,7 +11191,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR50">
         <v>0.79</v>
@@ -11600,7 +11600,7 @@
         <v>0.6</v>
       </c>
       <c r="AP52">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52">
         <v>0.38</v>
@@ -13251,7 +13251,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR60">
         <v>2.23</v>
@@ -14072,7 +14072,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ64">
         <v>1.86</v>
@@ -15105,7 +15105,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ69">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR69">
         <v>1.56</v>
@@ -15514,7 +15514,7 @@
         <v>0.2</v>
       </c>
       <c r="AP71">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ71">
         <v>0.57</v>
@@ -17859,6 +17859,212 @@
       </c>
       <c r="BP82">
         <v>1.73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7796949</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45843.54166666666</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s">
+        <v>74</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
+        <v>85</v>
+      </c>
+      <c r="P83" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q83">
+        <v>4.1</v>
+      </c>
+      <c r="R83">
+        <v>2.38</v>
+      </c>
+      <c r="S83">
+        <v>2.31</v>
+      </c>
+      <c r="T83">
+        <v>1.28</v>
+      </c>
+      <c r="U83">
+        <v>3.4</v>
+      </c>
+      <c r="V83">
+        <v>2.22</v>
+      </c>
+      <c r="W83">
+        <v>1.57</v>
+      </c>
+      <c r="X83">
+        <v>5</v>
+      </c>
+      <c r="Y83">
+        <v>1.15</v>
+      </c>
+      <c r="Z83">
+        <v>4.2</v>
+      </c>
+      <c r="AA83">
+        <v>3.8</v>
+      </c>
+      <c r="AB83">
+        <v>1.61</v>
+      </c>
+      <c r="AC83">
+        <v>1.03</v>
+      </c>
+      <c r="AD83">
+        <v>15</v>
+      </c>
+      <c r="AE83">
+        <v>1.17</v>
+      </c>
+      <c r="AF83">
+        <v>4.75</v>
+      </c>
+      <c r="AG83">
+        <v>1.47</v>
+      </c>
+      <c r="AH83">
+        <v>2.3</v>
+      </c>
+      <c r="AI83">
+        <v>1.55</v>
+      </c>
+      <c r="AJ83">
+        <v>2.25</v>
+      </c>
+      <c r="AK83">
+        <v>1.25</v>
+      </c>
+      <c r="AL83">
+        <v>1.2</v>
+      </c>
+      <c r="AM83">
+        <v>1.22</v>
+      </c>
+      <c r="AN83">
+        <v>1.17</v>
+      </c>
+      <c r="AO83">
+        <v>1.33</v>
+      </c>
+      <c r="AP83">
+        <v>1.14</v>
+      </c>
+      <c r="AQ83">
+        <v>1.29</v>
+      </c>
+      <c r="AR83">
+        <v>1.22</v>
+      </c>
+      <c r="AS83">
+        <v>1.51</v>
+      </c>
+      <c r="AT83">
+        <v>2.73</v>
+      </c>
+      <c r="AU83">
+        <v>3</v>
+      </c>
+      <c r="AV83">
+        <v>3</v>
+      </c>
+      <c r="AW83">
+        <v>3</v>
+      </c>
+      <c r="AX83">
+        <v>7</v>
+      </c>
+      <c r="AY83">
+        <v>6</v>
+      </c>
+      <c r="AZ83">
+        <v>10</v>
+      </c>
+      <c r="BA83">
+        <v>3</v>
+      </c>
+      <c r="BB83">
+        <v>9</v>
+      </c>
+      <c r="BC83">
+        <v>12</v>
+      </c>
+      <c r="BD83">
+        <v>2.85</v>
+      </c>
+      <c r="BE83">
+        <v>9.5</v>
+      </c>
+      <c r="BF83">
+        <v>1.54</v>
+      </c>
+      <c r="BG83">
+        <v>1.02</v>
+      </c>
+      <c r="BH83">
+        <v>6.74</v>
+      </c>
+      <c r="BI83">
+        <v>1.14</v>
+      </c>
+      <c r="BJ83">
+        <v>4.18</v>
+      </c>
+      <c r="BK83">
+        <v>1.41</v>
+      </c>
+      <c r="BL83">
+        <v>2.89</v>
+      </c>
+      <c r="BM83">
+        <v>1.7</v>
+      </c>
+      <c r="BN83">
+        <v>2.05</v>
+      </c>
+      <c r="BO83">
+        <v>1.95</v>
+      </c>
+      <c r="BP83">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -18001,22 +18001,22 @@
         <v>2.73</v>
       </c>
       <c r="AU83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX83">
+        <v>8</v>
+      </c>
+      <c r="AY83">
         <v>7</v>
       </c>
-      <c r="AY83">
-        <v>6</v>
-      </c>
       <c r="AZ83">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA83">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="199">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -457,6 +457,9 @@
     <t>['44', '47']</t>
   </si>
   <si>
+    <t>['71']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -605,6 +608,9 @@
   </si>
   <si>
     <t>['18', '77']</t>
+  </si>
+  <si>
+    <t>['69', '65']</t>
   </si>
 </sst>
 </file>
@@ -966,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP83"/>
+  <dimension ref="A1:BP84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1428,7 +1434,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1634,7 +1640,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1840,7 +1846,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2951,7 +2957,7 @@
         <v>3</v>
       </c>
       <c r="AQ10">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>1.61</v>
@@ -3076,7 +3082,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3488,7 +3494,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3566,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ13">
         <v>1.43</v>
@@ -3694,7 +3700,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3775,7 +3781,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>2.07</v>
@@ -3900,7 +3906,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4106,7 +4112,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4312,7 +4318,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4518,7 +4524,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4930,7 +4936,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5136,7 +5142,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5420,7 +5426,7 @@
         <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ22">
         <v>1.13</v>
@@ -5548,7 +5554,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5960,7 +5966,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6166,7 +6172,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6453,7 +6459,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ27">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.96</v>
@@ -6990,7 +6996,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7196,7 +7202,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7608,7 +7614,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7686,7 +7692,7 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -7814,7 +7820,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8226,7 +8232,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8925,7 +8931,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ39">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.45</v>
@@ -9050,7 +9056,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9256,7 +9262,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9462,7 +9468,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9668,7 +9674,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9874,7 +9880,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -9952,7 +9958,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10492,7 +10498,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10698,7 +10704,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11110,7 +11116,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11316,7 +11322,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11522,7 +11528,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11728,7 +11734,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11809,7 +11815,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ53">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -11934,7 +11940,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12140,7 +12146,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12424,7 +12430,7 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ56">
         <v>1.17</v>
@@ -12964,7 +12970,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13376,7 +13382,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13582,7 +13588,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13869,7 +13875,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>0.93</v>
@@ -13994,7 +14000,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14406,7 +14412,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14612,7 +14618,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -15024,7 +15030,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15230,7 +15236,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15436,7 +15442,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15642,7 +15648,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16054,7 +16060,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16260,7 +16266,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16672,7 +16678,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16878,7 +16884,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17084,7 +17090,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17162,7 +17168,7 @@
         <v>0.43</v>
       </c>
       <c r="AP79">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ79">
         <v>0.38</v>
@@ -17290,7 +17296,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17496,7 +17502,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18065,6 +18071,212 @@
       </c>
       <c r="BP83">
         <v>1.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7796950</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45844.54166666666</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
+        <v>78</v>
+      </c>
+      <c r="H84" t="s">
+        <v>72</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>3</v>
+      </c>
+      <c r="O84" t="s">
+        <v>147</v>
+      </c>
+      <c r="P84" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q84">
+        <v>2.23</v>
+      </c>
+      <c r="R84">
+        <v>2.66</v>
+      </c>
+      <c r="S84">
+        <v>3.4</v>
+      </c>
+      <c r="T84">
+        <v>1.16</v>
+      </c>
+      <c r="U84">
+        <v>4.5</v>
+      </c>
+      <c r="V84">
+        <v>1.98</v>
+      </c>
+      <c r="W84">
+        <v>1.97</v>
+      </c>
+      <c r="X84">
+        <v>3.6</v>
+      </c>
+      <c r="Y84">
+        <v>1.25</v>
+      </c>
+      <c r="Z84">
+        <v>1.68</v>
+      </c>
+      <c r="AA84">
+        <v>4.55</v>
+      </c>
+      <c r="AB84">
+        <v>3.75</v>
+      </c>
+      <c r="AC84">
+        <v>1.01</v>
+      </c>
+      <c r="AD84">
+        <v>26</v>
+      </c>
+      <c r="AE84">
+        <v>1.08</v>
+      </c>
+      <c r="AF84">
+        <v>7.5</v>
+      </c>
+      <c r="AG84">
+        <v>1.3</v>
+      </c>
+      <c r="AH84">
+        <v>3.5</v>
+      </c>
+      <c r="AI84">
+        <v>1.36</v>
+      </c>
+      <c r="AJ84">
+        <v>2.9</v>
+      </c>
+      <c r="AK84">
+        <v>1.22</v>
+      </c>
+      <c r="AL84">
+        <v>1.19</v>
+      </c>
+      <c r="AM84">
+        <v>2</v>
+      </c>
+      <c r="AN84">
+        <v>2.17</v>
+      </c>
+      <c r="AO84">
+        <v>0.67</v>
+      </c>
+      <c r="AP84">
+        <v>1.86</v>
+      </c>
+      <c r="AQ84">
+        <v>1</v>
+      </c>
+      <c r="AR84">
+        <v>1.96</v>
+      </c>
+      <c r="AS84">
+        <v>1.88</v>
+      </c>
+      <c r="AT84">
+        <v>3.84</v>
+      </c>
+      <c r="AU84">
+        <v>6</v>
+      </c>
+      <c r="AV84">
+        <v>5</v>
+      </c>
+      <c r="AW84">
+        <v>6</v>
+      </c>
+      <c r="AX84">
+        <v>6</v>
+      </c>
+      <c r="AY84">
+        <v>12</v>
+      </c>
+      <c r="AZ84">
+        <v>11</v>
+      </c>
+      <c r="BA84">
+        <v>6</v>
+      </c>
+      <c r="BB84">
+        <v>6</v>
+      </c>
+      <c r="BC84">
+        <v>12</v>
+      </c>
+      <c r="BD84">
+        <v>1.67</v>
+      </c>
+      <c r="BE84">
+        <v>9.5</v>
+      </c>
+      <c r="BF84">
+        <v>2.5</v>
+      </c>
+      <c r="BG84">
+        <v>1.01</v>
+      </c>
+      <c r="BH84">
+        <v>7.07</v>
+      </c>
+      <c r="BI84">
+        <v>1.12</v>
+      </c>
+      <c r="BJ84">
+        <v>4.33</v>
+      </c>
+      <c r="BK84">
+        <v>1.3</v>
+      </c>
+      <c r="BL84">
+        <v>3.28</v>
+      </c>
+      <c r="BM84">
+        <v>1.46</v>
+      </c>
+      <c r="BN84">
+        <v>2.45</v>
+      </c>
+      <c r="BO84">
+        <v>1.78</v>
+      </c>
+      <c r="BP84">
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -18219,16 +18219,16 @@
         <v>5</v>
       </c>
       <c r="AW84">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX84">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY84">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ84">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA84">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="200">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>['71']</t>
+  </si>
+  <si>
+    <t>['57']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -972,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP84"/>
+  <dimension ref="A1:BP85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1434,7 +1437,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1640,7 +1643,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1846,7 +1849,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -3082,7 +3085,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3494,7 +3497,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3700,7 +3703,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3906,7 +3909,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4112,7 +4115,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4190,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.43</v>
@@ -4318,7 +4321,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4399,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>2.7</v>
@@ -4524,7 +4527,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4936,7 +4939,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5142,7 +5145,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5554,7 +5557,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5966,7 +5969,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6172,7 +6175,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6662,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>1.43</v>
@@ -6871,7 +6874,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR29">
         <v>1.52</v>
@@ -6996,7 +6999,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7202,7 +7205,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7614,7 +7617,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7820,7 +7823,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8232,7 +8235,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -9056,7 +9059,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9262,7 +9265,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9468,7 +9471,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9674,7 +9677,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9880,7 +9883,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10498,7 +10501,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10579,7 +10582,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR47">
         <v>0.74</v>
@@ -10704,7 +10707,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10988,7 +10991,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>1.86</v>
@@ -11116,7 +11119,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11322,7 +11325,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11528,7 +11531,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11734,7 +11737,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11940,7 +11943,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12146,7 +12149,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12639,7 +12642,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ57">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -12842,7 +12845,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>0.57</v>
@@ -12970,7 +12973,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13382,7 +13385,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13588,7 +13591,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -14000,7 +14003,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14412,7 +14415,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14618,7 +14621,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14902,7 +14905,7 @@
         <v>1.4</v>
       </c>
       <c r="AP68">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -15030,7 +15033,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15236,7 +15239,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15317,7 +15320,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15442,7 +15445,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15648,7 +15651,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16060,7 +16063,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16266,7 +16269,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16678,7 +16681,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16884,7 +16887,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17090,7 +17093,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17296,7 +17299,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17502,7 +17505,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18120,7 +18123,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -18277,6 +18280,212 @@
       </c>
       <c r="BP84">
         <v>1.93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7796951</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45845.67708333334</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s">
+        <v>75</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>2</v>
+      </c>
+      <c r="O85" t="s">
+        <v>148</v>
+      </c>
+      <c r="P85" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q85">
+        <v>2.62</v>
+      </c>
+      <c r="R85">
+        <v>2.38</v>
+      </c>
+      <c r="S85">
+        <v>3.3</v>
+      </c>
+      <c r="T85">
+        <v>1.22</v>
+      </c>
+      <c r="U85">
+        <v>3.75</v>
+      </c>
+      <c r="V85">
+        <v>2.15</v>
+      </c>
+      <c r="W85">
+        <v>1.62</v>
+      </c>
+      <c r="X85">
+        <v>5</v>
+      </c>
+      <c r="Y85">
+        <v>1.17</v>
+      </c>
+      <c r="Z85">
+        <v>2</v>
+      </c>
+      <c r="AA85">
+        <v>3.86</v>
+      </c>
+      <c r="AB85">
+        <v>2.98</v>
+      </c>
+      <c r="AC85">
+        <v>1.02</v>
+      </c>
+      <c r="AD85">
+        <v>14</v>
+      </c>
+      <c r="AE85">
+        <v>1.15</v>
+      </c>
+      <c r="AF85">
+        <v>5.3</v>
+      </c>
+      <c r="AG85">
+        <v>1.52</v>
+      </c>
+      <c r="AH85">
+        <v>2.4</v>
+      </c>
+      <c r="AI85">
+        <v>1.4</v>
+      </c>
+      <c r="AJ85">
+        <v>2.6</v>
+      </c>
+      <c r="AK85">
+        <v>1.25</v>
+      </c>
+      <c r="AL85">
+        <v>1.25</v>
+      </c>
+      <c r="AM85">
+        <v>1.67</v>
+      </c>
+      <c r="AN85">
+        <v>2.2</v>
+      </c>
+      <c r="AO85">
+        <v>0.8</v>
+      </c>
+      <c r="AP85">
+        <v>2</v>
+      </c>
+      <c r="AQ85">
+        <v>0.83</v>
+      </c>
+      <c r="AR85">
+        <v>1.65</v>
+      </c>
+      <c r="AS85">
+        <v>1.58</v>
+      </c>
+      <c r="AT85">
+        <v>3.23</v>
+      </c>
+      <c r="AU85">
+        <v>8</v>
+      </c>
+      <c r="AV85">
+        <v>7</v>
+      </c>
+      <c r="AW85">
+        <v>8</v>
+      </c>
+      <c r="AX85">
+        <v>6</v>
+      </c>
+      <c r="AY85">
+        <v>16</v>
+      </c>
+      <c r="AZ85">
+        <v>13</v>
+      </c>
+      <c r="BA85">
+        <v>6</v>
+      </c>
+      <c r="BB85">
+        <v>7</v>
+      </c>
+      <c r="BC85">
+        <v>13</v>
+      </c>
+      <c r="BD85">
+        <v>1.64</v>
+      </c>
+      <c r="BE85">
+        <v>8.75</v>
+      </c>
+      <c r="BF85">
+        <v>3.24</v>
+      </c>
+      <c r="BG85">
+        <v>1.01</v>
+      </c>
+      <c r="BH85">
+        <v>7.17</v>
+      </c>
+      <c r="BI85">
+        <v>1.05</v>
+      </c>
+      <c r="BJ85">
+        <v>5.89</v>
+      </c>
+      <c r="BK85">
+        <v>1.22</v>
+      </c>
+      <c r="BL85">
+        <v>3.82</v>
+      </c>
+      <c r="BM85">
+        <v>1.48</v>
+      </c>
+      <c r="BN85">
+        <v>2.74</v>
+      </c>
+      <c r="BO85">
+        <v>1.78</v>
+      </c>
+      <c r="BP85">
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -18425,19 +18425,19 @@
         <v>8</v>
       </c>
       <c r="AV85">
+        <v>6</v>
+      </c>
+      <c r="AW85">
         <v>7</v>
       </c>
-      <c r="AW85">
-        <v>8</v>
-      </c>
       <c r="AX85">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY85">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ85">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA85">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="200">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -975,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP85"/>
+  <dimension ref="A1:BP87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1724,7 +1724,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ15">
         <v>1.17</v>
@@ -4196,7 +4196,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR17">
         <v>2.7</v>
@@ -4605,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -6253,7 +6253,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ26">
         <v>1.17</v>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6874,7 +6874,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR29">
         <v>1.52</v>
@@ -7080,7 +7080,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR30">
         <v>2.63</v>
@@ -8931,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9140,7 +9140,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR40">
         <v>1.47</v>
@@ -9755,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ43">
         <v>0.38</v>
@@ -10582,7 +10582,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR47">
         <v>0.74</v>
@@ -11609,7 +11609,7 @@
         <v>0.6</v>
       </c>
       <c r="AP52">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52">
         <v>0.38</v>
@@ -12230,7 +12230,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR55">
         <v>1.56</v>
@@ -12642,7 +12642,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ57">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -13051,7 +13051,7 @@
         <v>0.8</v>
       </c>
       <c r="AP59">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -14081,7 +14081,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ64">
         <v>1.86</v>
@@ -14702,7 +14702,7 @@
         <v>3</v>
       </c>
       <c r="AQ67">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR67">
         <v>1.75</v>
@@ -15317,10 +15317,10 @@
         <v>0.25</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ70">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15523,7 +15523,7 @@
         <v>0.2</v>
       </c>
       <c r="AP71">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
         <v>0.57</v>
@@ -15732,7 +15732,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ72">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR72">
         <v>2.2</v>
@@ -17789,7 +17789,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ83">
         <v>1.29</v>
@@ -18410,7 +18410,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR85">
         <v>1.65</v>
@@ -18486,6 +18486,418 @@
       </c>
       <c r="BP85">
         <v>2.12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7796952</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45852.64583333334</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>81</v>
+      </c>
+      <c r="H86" t="s">
+        <v>75</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
+        <v>147</v>
+      </c>
+      <c r="P86" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q86">
+        <v>3.12</v>
+      </c>
+      <c r="R86">
+        <v>2.49</v>
+      </c>
+      <c r="S86">
+        <v>2.9</v>
+      </c>
+      <c r="T86">
+        <v>1.25</v>
+      </c>
+      <c r="U86">
+        <v>3.7</v>
+      </c>
+      <c r="V86">
+        <v>2.25</v>
+      </c>
+      <c r="W86">
+        <v>1.6</v>
+      </c>
+      <c r="X86">
+        <v>4.6</v>
+      </c>
+      <c r="Y86">
+        <v>1.15</v>
+      </c>
+      <c r="Z86">
+        <v>3</v>
+      </c>
+      <c r="AA86">
+        <v>3.6</v>
+      </c>
+      <c r="AB86">
+        <v>2.44</v>
+      </c>
+      <c r="AC86">
+        <v>1.03</v>
+      </c>
+      <c r="AD86">
+        <v>12</v>
+      </c>
+      <c r="AE86">
+        <v>1.13</v>
+      </c>
+      <c r="AF86">
+        <v>5</v>
+      </c>
+      <c r="AG86">
+        <v>1.5</v>
+      </c>
+      <c r="AH86">
+        <v>2.45</v>
+      </c>
+      <c r="AI86">
+        <v>1.42</v>
+      </c>
+      <c r="AJ86">
+        <v>2.5</v>
+      </c>
+      <c r="AK86">
+        <v>1.48</v>
+      </c>
+      <c r="AL86">
+        <v>1.29</v>
+      </c>
+      <c r="AM86">
+        <v>1.44</v>
+      </c>
+      <c r="AN86">
+        <v>1.14</v>
+      </c>
+      <c r="AO86">
+        <v>0.83</v>
+      </c>
+      <c r="AP86">
+        <v>1.38</v>
+      </c>
+      <c r="AQ86">
+        <v>0.71</v>
+      </c>
+      <c r="AR86">
+        <v>1.16</v>
+      </c>
+      <c r="AS86">
+        <v>1.55</v>
+      </c>
+      <c r="AT86">
+        <v>2.71</v>
+      </c>
+      <c r="AU86">
+        <v>7</v>
+      </c>
+      <c r="AV86">
+        <v>3</v>
+      </c>
+      <c r="AW86">
+        <v>7</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+      <c r="AY86">
+        <v>14</v>
+      </c>
+      <c r="AZ86">
+        <v>11</v>
+      </c>
+      <c r="BA86">
+        <v>5</v>
+      </c>
+      <c r="BB86">
+        <v>5</v>
+      </c>
+      <c r="BC86">
+        <v>10</v>
+      </c>
+      <c r="BD86">
+        <v>1.93</v>
+      </c>
+      <c r="BE86">
+        <v>9.4</v>
+      </c>
+      <c r="BF86">
+        <v>2.18</v>
+      </c>
+      <c r="BG86">
+        <v>0</v>
+      </c>
+      <c r="BH86">
+        <v>0</v>
+      </c>
+      <c r="BI86">
+        <v>1.09</v>
+      </c>
+      <c r="BJ86">
+        <v>5.34</v>
+      </c>
+      <c r="BK86">
+        <v>1.26</v>
+      </c>
+      <c r="BL86">
+        <v>3.53</v>
+      </c>
+      <c r="BM86">
+        <v>1.42</v>
+      </c>
+      <c r="BN86">
+        <v>2.64</v>
+      </c>
+      <c r="BO86">
+        <v>1.77</v>
+      </c>
+      <c r="BP86">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7796954</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45852.67708333334</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s">
+        <v>78</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87" t="s">
+        <v>147</v>
+      </c>
+      <c r="P87" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q87">
+        <v>3.86</v>
+      </c>
+      <c r="R87">
+        <v>2.65</v>
+      </c>
+      <c r="S87">
+        <v>1.93</v>
+      </c>
+      <c r="T87">
+        <v>1.14</v>
+      </c>
+      <c r="U87">
+        <v>5</v>
+      </c>
+      <c r="V87">
+        <v>1.65</v>
+      </c>
+      <c r="W87">
+        <v>2.11</v>
+      </c>
+      <c r="X87">
+        <v>3.1</v>
+      </c>
+      <c r="Y87">
+        <v>1.33</v>
+      </c>
+      <c r="Z87">
+        <v>3.75</v>
+      </c>
+      <c r="AA87">
+        <v>4.62</v>
+      </c>
+      <c r="AB87">
+        <v>1.7</v>
+      </c>
+      <c r="AC87">
+        <v>1</v>
+      </c>
+      <c r="AD87">
+        <v>29</v>
+      </c>
+      <c r="AE87">
+        <v>1.02</v>
+      </c>
+      <c r="AF87">
+        <v>9.5</v>
+      </c>
+      <c r="AG87">
+        <v>1.2</v>
+      </c>
+      <c r="AH87">
+        <v>3.9</v>
+      </c>
+      <c r="AI87">
+        <v>1.25</v>
+      </c>
+      <c r="AJ87">
+        <v>3.75</v>
+      </c>
+      <c r="AK87">
+        <v>2.1</v>
+      </c>
+      <c r="AL87">
+        <v>1.2</v>
+      </c>
+      <c r="AM87">
+        <v>1.25</v>
+      </c>
+      <c r="AN87">
+        <v>0.5</v>
+      </c>
+      <c r="AO87">
+        <v>0.43</v>
+      </c>
+      <c r="AP87">
+        <v>0.86</v>
+      </c>
+      <c r="AQ87">
+        <v>0.38</v>
+      </c>
+      <c r="AR87">
+        <v>1.67</v>
+      </c>
+      <c r="AS87">
+        <v>1.88</v>
+      </c>
+      <c r="AT87">
+        <v>3.55</v>
+      </c>
+      <c r="AU87">
+        <v>4</v>
+      </c>
+      <c r="AV87">
+        <v>5</v>
+      </c>
+      <c r="AW87">
+        <v>1</v>
+      </c>
+      <c r="AX87">
+        <v>6</v>
+      </c>
+      <c r="AY87">
+        <v>5</v>
+      </c>
+      <c r="AZ87">
+        <v>11</v>
+      </c>
+      <c r="BA87">
+        <v>0</v>
+      </c>
+      <c r="BB87">
+        <v>8</v>
+      </c>
+      <c r="BC87">
+        <v>8</v>
+      </c>
+      <c r="BD87">
+        <v>3.42</v>
+      </c>
+      <c r="BE87">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF87">
+        <v>1.56</v>
+      </c>
+      <c r="BG87">
+        <v>1.01</v>
+      </c>
+      <c r="BH87">
+        <v>7.12</v>
+      </c>
+      <c r="BI87">
+        <v>1.08</v>
+      </c>
+      <c r="BJ87">
+        <v>4.95</v>
+      </c>
+      <c r="BK87">
+        <v>1.28</v>
+      </c>
+      <c r="BL87">
+        <v>3.42</v>
+      </c>
+      <c r="BM87">
+        <v>1.43</v>
+      </c>
+      <c r="BN87">
+        <v>2.5</v>
+      </c>
+      <c r="BO87">
+        <v>1.74</v>
+      </c>
+      <c r="BP87">
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -18628,22 +18628,22 @@
         <v>2.71</v>
       </c>
       <c r="AU86">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW86">
         <v>7</v>
       </c>
       <c r="AX86">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY86">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ86">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA86">
         <v>5</v>
@@ -18834,31 +18834,31 @@
         <v>3.55</v>
       </c>
       <c r="AU87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV87">
+        <v>9</v>
+      </c>
+      <c r="AW87">
         <v>5</v>
       </c>
-      <c r="AW87">
-        <v>1</v>
-      </c>
       <c r="AX87">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY87">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AZ87">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB87">
         <v>8</v>
       </c>
       <c r="BC87">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD87">
         <v>3.42</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="201">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['70']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -1437,7 +1440,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1643,7 +1646,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1849,7 +1852,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -3085,7 +3088,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3497,7 +3500,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3703,7 +3706,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3909,7 +3912,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4115,7 +4118,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4321,7 +4324,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4527,7 +4530,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4939,7 +4942,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5145,7 +5148,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5557,7 +5560,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5969,7 +5972,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6175,7 +6178,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6999,7 +7002,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7205,7 +7208,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7617,7 +7620,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7823,7 +7826,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8235,7 +8238,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -9059,7 +9062,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9265,7 +9268,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9471,7 +9474,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9677,7 +9680,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9883,7 +9886,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10501,7 +10504,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10707,7 +10710,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11119,7 +11122,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11325,7 +11328,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11531,7 +11534,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11737,7 +11740,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11943,7 +11946,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12149,7 +12152,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12973,7 +12976,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13385,7 +13388,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13591,7 +13594,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -14003,7 +14006,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14415,7 +14418,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14621,7 +14624,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -15033,7 +15036,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15239,7 +15242,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15445,7 +15448,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15651,7 +15654,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16063,7 +16066,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16269,7 +16272,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16681,7 +16684,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16887,7 +16890,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17093,7 +17096,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17299,7 +17302,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17505,7 +17508,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18123,7 +18126,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -18631,19 +18634,19 @@
         <v>6</v>
       </c>
       <c r="AV86">
+        <v>3</v>
+      </c>
+      <c r="AW86">
         <v>4</v>
       </c>
-      <c r="AW86">
+      <c r="AX86">
+        <v>4</v>
+      </c>
+      <c r="AY86">
+        <v>10</v>
+      </c>
+      <c r="AZ86">
         <v>7</v>
-      </c>
-      <c r="AX86">
-        <v>5</v>
-      </c>
-      <c r="AY86">
-        <v>13</v>
-      </c>
-      <c r="AZ86">
-        <v>9</v>
       </c>
       <c r="BA86">
         <v>5</v>
@@ -18738,7 +18741,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P87" t="s">
         <v>85</v>
@@ -18834,22 +18837,22 @@
         <v>3.55</v>
       </c>
       <c r="AU87">
+        <v>5</v>
+      </c>
+      <c r="AV87">
+        <v>8</v>
+      </c>
+      <c r="AW87">
+        <v>1</v>
+      </c>
+      <c r="AX87">
         <v>3</v>
       </c>
-      <c r="AV87">
-        <v>9</v>
-      </c>
-      <c r="AW87">
-        <v>5</v>
-      </c>
-      <c r="AX87">
-        <v>8</v>
-      </c>
       <c r="AY87">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ87">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA87">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -18634,19 +18634,19 @@
         <v>6</v>
       </c>
       <c r="AV86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW86">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY86">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ86">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA86">
         <v>5</v>
@@ -18837,22 +18837,22 @@
         <v>3.55</v>
       </c>
       <c r="AU87">
+        <v>3</v>
+      </c>
+      <c r="AV87">
+        <v>9</v>
+      </c>
+      <c r="AW87">
         <v>5</v>
       </c>
-      <c r="AV87">
+      <c r="AX87">
         <v>8</v>
       </c>
-      <c r="AW87">
-        <v>1</v>
-      </c>
-      <c r="AX87">
-        <v>3</v>
-      </c>
       <c r="AY87">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ87">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA87">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="202">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['17', '42', '65', '67', '78']</t>
   </si>
   <si>
     <t>['70']</t>
@@ -978,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP87"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1440,7 +1443,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1646,7 +1649,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1852,7 +1855,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2963,7 +2966,7 @@
         <v>3</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR10">
         <v>1.61</v>
@@ -3088,7 +3091,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3500,7 +3503,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3706,7 +3709,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3787,7 +3790,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR14">
         <v>2.07</v>
@@ -3912,7 +3915,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4118,7 +4121,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4196,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ16">
         <v>0.38</v>
@@ -4324,7 +4327,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4530,7 +4533,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4942,7 +4945,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5148,7 +5151,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5560,7 +5563,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5972,7 +5975,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6178,7 +6181,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6465,7 +6468,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR27">
         <v>1.96</v>
@@ -6668,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ28">
         <v>1.43</v>
@@ -7002,7 +7005,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7208,7 +7211,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7620,7 +7623,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7826,7 +7829,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8238,7 +8241,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8937,7 +8940,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR39">
         <v>1.45</v>
@@ -9062,7 +9065,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9268,7 +9271,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9474,7 +9477,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9680,7 +9683,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9886,7 +9889,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10504,7 +10507,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10710,7 +10713,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10994,7 +10997,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ49">
         <v>1.86</v>
@@ -11122,7 +11125,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11328,7 +11331,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11534,7 +11537,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11740,7 +11743,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11821,7 +11824,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -11946,7 +11949,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12152,7 +12155,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12848,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ58">
         <v>0.57</v>
@@ -12976,7 +12979,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13388,7 +13391,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13594,7 +13597,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13881,7 +13884,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR63">
         <v>0.93</v>
@@ -14006,7 +14009,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14418,7 +14421,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14624,7 +14627,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14908,7 +14911,7 @@
         <v>1.4</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -15036,7 +15039,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15242,7 +15245,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15448,7 +15451,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15654,7 +15657,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16066,7 +16069,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16272,7 +16275,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16684,7 +16687,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16890,7 +16893,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17096,7 +17099,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17302,7 +17305,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17508,7 +17511,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18126,7 +18129,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -18207,7 +18210,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR84">
         <v>1.96</v>
@@ -18410,7 +18413,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ85">
         <v>0.71</v>
@@ -18496,7 +18499,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>7796952</v>
+        <v>7796956</v>
       </c>
       <c r="C86" t="s">
         <v>68</v>
@@ -18505,166 +18508,166 @@
         <v>69</v>
       </c>
       <c r="E86" s="2">
-        <v>45852.64583333334</v>
+        <v>45851.54166666666</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M86">
         <v>0</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O86" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P86" t="s">
         <v>85</v>
       </c>
       <c r="Q86">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S86">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86">
+        <v>0</v>
+      </c>
+      <c r="AD86">
+        <v>0</v>
+      </c>
+      <c r="AE86">
+        <v>0</v>
+      </c>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>0</v>
+      </c>
+      <c r="AH86">
+        <v>0</v>
+      </c>
+      <c r="AI86">
+        <v>0</v>
+      </c>
+      <c r="AJ86">
+        <v>0</v>
+      </c>
+      <c r="AK86">
+        <v>0</v>
+      </c>
+      <c r="AL86">
+        <v>0</v>
+      </c>
+      <c r="AM86">
+        <v>0</v>
+      </c>
+      <c r="AN86">
+        <v>2</v>
+      </c>
+      <c r="AO86">
+        <v>1</v>
+      </c>
+      <c r="AP86">
+        <v>2.14</v>
+      </c>
+      <c r="AQ86">
+        <v>0.88</v>
+      </c>
+      <c r="AR86">
+        <v>1.71</v>
+      </c>
+      <c r="AS86">
+        <v>1.84</v>
+      </c>
+      <c r="AT86">
+        <v>3.55</v>
+      </c>
+      <c r="AU86">
+        <v>8</v>
+      </c>
+      <c r="AV86">
+        <v>5</v>
+      </c>
+      <c r="AW86">
+        <v>9</v>
+      </c>
+      <c r="AX86">
+        <v>6</v>
+      </c>
+      <c r="AY86">
+        <v>17</v>
+      </c>
+      <c r="AZ86">
+        <v>11</v>
+      </c>
+      <c r="BA86">
         <v>3</v>
-      </c>
-      <c r="AA86">
-        <v>3.6</v>
-      </c>
-      <c r="AB86">
-        <v>2.44</v>
-      </c>
-      <c r="AC86">
-        <v>1.03</v>
-      </c>
-      <c r="AD86">
-        <v>12</v>
-      </c>
-      <c r="AE86">
-        <v>1.13</v>
-      </c>
-      <c r="AF86">
-        <v>5</v>
-      </c>
-      <c r="AG86">
-        <v>1.5</v>
-      </c>
-      <c r="AH86">
-        <v>2.45</v>
-      </c>
-      <c r="AI86">
-        <v>1.42</v>
-      </c>
-      <c r="AJ86">
-        <v>2.5</v>
-      </c>
-      <c r="AK86">
-        <v>1.48</v>
-      </c>
-      <c r="AL86">
-        <v>1.29</v>
-      </c>
-      <c r="AM86">
-        <v>1.44</v>
-      </c>
-      <c r="AN86">
-        <v>1.14</v>
-      </c>
-      <c r="AO86">
-        <v>0.83</v>
-      </c>
-      <c r="AP86">
-        <v>1.38</v>
-      </c>
-      <c r="AQ86">
-        <v>0.71</v>
-      </c>
-      <c r="AR86">
-        <v>1.16</v>
-      </c>
-      <c r="AS86">
-        <v>1.55</v>
-      </c>
-      <c r="AT86">
-        <v>2.71</v>
-      </c>
-      <c r="AU86">
-        <v>6</v>
-      </c>
-      <c r="AV86">
-        <v>4</v>
-      </c>
-      <c r="AW86">
-        <v>7</v>
-      </c>
-      <c r="AX86">
-        <v>5</v>
-      </c>
-      <c r="AY86">
-        <v>13</v>
-      </c>
-      <c r="AZ86">
-        <v>9</v>
-      </c>
-      <c r="BA86">
-        <v>5</v>
       </c>
       <c r="BB86">
         <v>5</v>
       </c>
       <c r="BC86">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD86">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BE86">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BF86">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BG86">
         <v>0</v>
@@ -18673,28 +18676,28 @@
         <v>0</v>
       </c>
       <c r="BI86">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BJ86">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="BK86">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BL86">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="BM86">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BN86">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BO86">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BP86">
-        <v>1.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:68">
@@ -18702,7 +18705,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>7796954</v>
+        <v>7796952</v>
       </c>
       <c r="C87" t="s">
         <v>68</v>
@@ -18711,16 +18714,16 @@
         <v>69</v>
       </c>
       <c r="E87" s="2">
-        <v>45852.67708333334</v>
+        <v>45852.64583333334</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -18741,165 +18744,371 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P87" t="s">
         <v>85</v>
       </c>
       <c r="Q87">
+        <v>3.12</v>
+      </c>
+      <c r="R87">
+        <v>2.49</v>
+      </c>
+      <c r="S87">
+        <v>2.9</v>
+      </c>
+      <c r="T87">
+        <v>1.25</v>
+      </c>
+      <c r="U87">
+        <v>3.7</v>
+      </c>
+      <c r="V87">
+        <v>2.25</v>
+      </c>
+      <c r="W87">
+        <v>1.6</v>
+      </c>
+      <c r="X87">
+        <v>4.6</v>
+      </c>
+      <c r="Y87">
+        <v>1.15</v>
+      </c>
+      <c r="Z87">
+        <v>3</v>
+      </c>
+      <c r="AA87">
+        <v>3.6</v>
+      </c>
+      <c r="AB87">
+        <v>2.44</v>
+      </c>
+      <c r="AC87">
+        <v>1.03</v>
+      </c>
+      <c r="AD87">
+        <v>12</v>
+      </c>
+      <c r="AE87">
+        <v>1.13</v>
+      </c>
+      <c r="AF87">
+        <v>5</v>
+      </c>
+      <c r="AG87">
+        <v>1.5</v>
+      </c>
+      <c r="AH87">
+        <v>2.45</v>
+      </c>
+      <c r="AI87">
+        <v>1.42</v>
+      </c>
+      <c r="AJ87">
+        <v>2.5</v>
+      </c>
+      <c r="AK87">
+        <v>1.48</v>
+      </c>
+      <c r="AL87">
+        <v>1.29</v>
+      </c>
+      <c r="AM87">
+        <v>1.44</v>
+      </c>
+      <c r="AN87">
+        <v>1.14</v>
+      </c>
+      <c r="AO87">
+        <v>0.83</v>
+      </c>
+      <c r="AP87">
+        <v>1.38</v>
+      </c>
+      <c r="AQ87">
+        <v>0.71</v>
+      </c>
+      <c r="AR87">
+        <v>1.16</v>
+      </c>
+      <c r="AS87">
+        <v>1.55</v>
+      </c>
+      <c r="AT87">
+        <v>2.71</v>
+      </c>
+      <c r="AU87">
+        <v>6</v>
+      </c>
+      <c r="AV87">
+        <v>4</v>
+      </c>
+      <c r="AW87">
+        <v>7</v>
+      </c>
+      <c r="AX87">
+        <v>5</v>
+      </c>
+      <c r="AY87">
+        <v>13</v>
+      </c>
+      <c r="AZ87">
+        <v>9</v>
+      </c>
+      <c r="BA87">
+        <v>5</v>
+      </c>
+      <c r="BB87">
+        <v>5</v>
+      </c>
+      <c r="BC87">
+        <v>10</v>
+      </c>
+      <c r="BD87">
+        <v>1.93</v>
+      </c>
+      <c r="BE87">
+        <v>9.4</v>
+      </c>
+      <c r="BF87">
+        <v>2.18</v>
+      </c>
+      <c r="BG87">
+        <v>0</v>
+      </c>
+      <c r="BH87">
+        <v>0</v>
+      </c>
+      <c r="BI87">
+        <v>1.09</v>
+      </c>
+      <c r="BJ87">
+        <v>5.34</v>
+      </c>
+      <c r="BK87">
+        <v>1.26</v>
+      </c>
+      <c r="BL87">
+        <v>3.53</v>
+      </c>
+      <c r="BM87">
+        <v>1.42</v>
+      </c>
+      <c r="BN87">
+        <v>2.64</v>
+      </c>
+      <c r="BO87">
+        <v>1.77</v>
+      </c>
+      <c r="BP87">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7796954</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45852.67708333334</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s">
+        <v>78</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88" t="s">
+        <v>150</v>
+      </c>
+      <c r="P88" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q88">
         <v>3.86</v>
       </c>
-      <c r="R87">
+      <c r="R88">
         <v>2.65</v>
       </c>
-      <c r="S87">
+      <c r="S88">
         <v>1.93</v>
       </c>
-      <c r="T87">
+      <c r="T88">
         <v>1.14</v>
       </c>
-      <c r="U87">
+      <c r="U88">
         <v>5</v>
       </c>
-      <c r="V87">
+      <c r="V88">
         <v>1.65</v>
       </c>
-      <c r="W87">
+      <c r="W88">
         <v>2.11</v>
       </c>
-      <c r="X87">
+      <c r="X88">
         <v>3.1</v>
       </c>
-      <c r="Y87">
+      <c r="Y88">
         <v>1.33</v>
       </c>
-      <c r="Z87">
+      <c r="Z88">
         <v>3.75</v>
       </c>
-      <c r="AA87">
+      <c r="AA88">
         <v>4.62</v>
       </c>
-      <c r="AB87">
+      <c r="AB88">
         <v>1.7</v>
       </c>
-      <c r="AC87">
-        <v>1</v>
-      </c>
-      <c r="AD87">
+      <c r="AC88">
+        <v>1</v>
+      </c>
+      <c r="AD88">
         <v>29</v>
       </c>
-      <c r="AE87">
+      <c r="AE88">
         <v>1.02</v>
       </c>
-      <c r="AF87">
+      <c r="AF88">
         <v>9.5</v>
       </c>
-      <c r="AG87">
+      <c r="AG88">
         <v>1.2</v>
       </c>
-      <c r="AH87">
+      <c r="AH88">
         <v>3.9</v>
       </c>
-      <c r="AI87">
+      <c r="AI88">
         <v>1.25</v>
       </c>
-      <c r="AJ87">
+      <c r="AJ88">
         <v>3.75</v>
       </c>
-      <c r="AK87">
+      <c r="AK88">
         <v>2.1</v>
       </c>
-      <c r="AL87">
+      <c r="AL88">
         <v>1.2</v>
       </c>
-      <c r="AM87">
+      <c r="AM88">
         <v>1.25</v>
       </c>
-      <c r="AN87">
+      <c r="AN88">
         <v>0.5</v>
       </c>
-      <c r="AO87">
+      <c r="AO88">
         <v>0.43</v>
       </c>
-      <c r="AP87">
+      <c r="AP88">
         <v>0.86</v>
       </c>
-      <c r="AQ87">
+      <c r="AQ88">
         <v>0.38</v>
       </c>
-      <c r="AR87">
+      <c r="AR88">
         <v>1.67</v>
       </c>
-      <c r="AS87">
+      <c r="AS88">
         <v>1.88</v>
       </c>
-      <c r="AT87">
+      <c r="AT88">
         <v>3.55</v>
       </c>
-      <c r="AU87">
+      <c r="AU88">
         <v>3</v>
       </c>
-      <c r="AV87">
+      <c r="AV88">
         <v>9</v>
       </c>
-      <c r="AW87">
+      <c r="AW88">
         <v>5</v>
       </c>
-      <c r="AX87">
+      <c r="AX88">
         <v>8</v>
       </c>
-      <c r="AY87">
+      <c r="AY88">
         <v>8</v>
       </c>
-      <c r="AZ87">
+      <c r="AZ88">
         <v>17</v>
       </c>
-      <c r="BA87">
-        <v>1</v>
-      </c>
-      <c r="BB87">
+      <c r="BA88">
+        <v>1</v>
+      </c>
+      <c r="BB88">
         <v>8</v>
       </c>
-      <c r="BC87">
+      <c r="BC88">
         <v>9</v>
       </c>
-      <c r="BD87">
+      <c r="BD88">
         <v>3.42</v>
       </c>
-      <c r="BE87">
+      <c r="BE88">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF87">
+      <c r="BF88">
         <v>1.56</v>
       </c>
-      <c r="BG87">
+      <c r="BG88">
         <v>1.01</v>
       </c>
-      <c r="BH87">
+      <c r="BH88">
         <v>7.12</v>
       </c>
-      <c r="BI87">
+      <c r="BI88">
         <v>1.08</v>
       </c>
-      <c r="BJ87">
+      <c r="BJ88">
         <v>4.95</v>
       </c>
-      <c r="BK87">
+      <c r="BK88">
         <v>1.28</v>
       </c>
-      <c r="BL87">
+      <c r="BL88">
         <v>3.42</v>
       </c>
-      <c r="BM87">
+      <c r="BM88">
         <v>1.43</v>
       </c>
-      <c r="BN87">
+      <c r="BN88">
         <v>2.5</v>
       </c>
-      <c r="BO87">
+      <c r="BO88">
         <v>1.74</v>
       </c>
-      <c r="BP87">
+      <c r="BP88">
         <v>1.98</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="203">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -467,6 +467,9 @@
   </si>
   <si>
     <t>['70']</t>
+  </si>
+  <si>
+    <t>['56']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -981,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1443,7 +1446,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1649,7 +1652,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1855,7 +1858,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2757,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3091,7 +3094,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3503,7 +3506,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3709,7 +3712,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3915,7 +3918,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4121,7 +4124,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4327,7 +4330,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4533,7 +4536,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4817,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ19">
         <v>1.29</v>
@@ -4945,7 +4948,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5151,7 +5154,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5563,7 +5566,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5975,7 +5978,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6181,7 +6184,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6877,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ29">
         <v>0.71</v>
@@ -7005,7 +7008,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7211,7 +7214,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7623,7 +7626,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7829,7 +7832,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8241,7 +8244,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -9065,7 +9068,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9143,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ40">
         <v>0.38</v>
@@ -9271,7 +9274,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9477,7 +9480,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9683,7 +9686,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9889,7 +9892,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10507,7 +10510,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10713,7 +10716,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11125,7 +11128,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11331,7 +11334,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11409,7 +11412,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ51">
         <v>1.43</v>
@@ -11537,7 +11540,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11743,7 +11746,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11949,7 +11952,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12155,7 +12158,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12979,7 +12982,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13391,7 +13394,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13597,7 +13600,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -14009,7 +14012,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14421,7 +14424,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14499,7 +14502,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ66">
         <v>1.13</v>
@@ -14627,7 +14630,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -15039,7 +15042,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15245,7 +15248,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15451,7 +15454,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15657,7 +15660,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16069,7 +16072,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16275,7 +16278,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16687,7 +16690,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16893,7 +16896,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17099,7 +17102,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17305,7 +17308,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17383,7 +17386,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ80">
         <v>1.86</v>
@@ -17511,7 +17514,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18129,7 +18132,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -19110,6 +19113,212 @@
       </c>
       <c r="BP88">
         <v>1.98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7796953</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45855.67708333334</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" t="s">
+        <v>73</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>2</v>
+      </c>
+      <c r="O89" t="s">
+        <v>151</v>
+      </c>
+      <c r="P89" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q89">
+        <v>3</v>
+      </c>
+      <c r="R89">
+        <v>2.43</v>
+      </c>
+      <c r="S89">
+        <v>2.95</v>
+      </c>
+      <c r="T89">
+        <v>1.29</v>
+      </c>
+      <c r="U89">
+        <v>3.3</v>
+      </c>
+      <c r="V89">
+        <v>2.38</v>
+      </c>
+      <c r="W89">
+        <v>1.52</v>
+      </c>
+      <c r="X89">
+        <v>5</v>
+      </c>
+      <c r="Y89">
+        <v>1.09</v>
+      </c>
+      <c r="Z89">
+        <v>2.4</v>
+      </c>
+      <c r="AA89">
+        <v>3.5</v>
+      </c>
+      <c r="AB89">
+        <v>2.48</v>
+      </c>
+      <c r="AC89">
+        <v>1.04</v>
+      </c>
+      <c r="AD89">
+        <v>12</v>
+      </c>
+      <c r="AE89">
+        <v>1.18</v>
+      </c>
+      <c r="AF89">
+        <v>4.4</v>
+      </c>
+      <c r="AG89">
+        <v>1.57</v>
+      </c>
+      <c r="AH89">
+        <v>2.25</v>
+      </c>
+      <c r="AI89">
+        <v>1.55</v>
+      </c>
+      <c r="AJ89">
+        <v>2.4</v>
+      </c>
+      <c r="AK89">
+        <v>1.27</v>
+      </c>
+      <c r="AL89">
+        <v>1.27</v>
+      </c>
+      <c r="AM89">
+        <v>1.44</v>
+      </c>
+      <c r="AN89">
+        <v>2</v>
+      </c>
+      <c r="AO89">
+        <v>1</v>
+      </c>
+      <c r="AP89">
+        <v>1.88</v>
+      </c>
+      <c r="AQ89">
+        <v>1</v>
+      </c>
+      <c r="AR89">
+        <v>1.61</v>
+      </c>
+      <c r="AS89">
+        <v>1.35</v>
+      </c>
+      <c r="AT89">
+        <v>2.96</v>
+      </c>
+      <c r="AU89">
+        <v>4</v>
+      </c>
+      <c r="AV89">
+        <v>6</v>
+      </c>
+      <c r="AW89">
+        <v>5</v>
+      </c>
+      <c r="AX89">
+        <v>6</v>
+      </c>
+      <c r="AY89">
+        <v>9</v>
+      </c>
+      <c r="AZ89">
+        <v>12</v>
+      </c>
+      <c r="BA89">
+        <v>6</v>
+      </c>
+      <c r="BB89">
+        <v>6</v>
+      </c>
+      <c r="BC89">
+        <v>12</v>
+      </c>
+      <c r="BD89">
+        <v>2.03</v>
+      </c>
+      <c r="BE89">
+        <v>7.75</v>
+      </c>
+      <c r="BF89">
+        <v>2.16</v>
+      </c>
+      <c r="BG89">
+        <v>1.06</v>
+      </c>
+      <c r="BH89">
+        <v>6.05</v>
+      </c>
+      <c r="BI89">
+        <v>1.22</v>
+      </c>
+      <c r="BJ89">
+        <v>4.15</v>
+      </c>
+      <c r="BK89">
+        <v>1.38</v>
+      </c>
+      <c r="BL89">
+        <v>2.89</v>
+      </c>
+      <c r="BM89">
+        <v>1.6</v>
+      </c>
+      <c r="BN89">
+        <v>2.19</v>
+      </c>
+      <c r="BO89">
+        <v>1.94</v>
+      </c>
+      <c r="BP89">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -19255,7 +19255,7 @@
         <v>2.96</v>
       </c>
       <c r="AU89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV89">
         <v>6</v>
@@ -19264,13 +19264,13 @@
         <v>5</v>
       </c>
       <c r="AX89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY89">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ89">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA89">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -19255,22 +19255,22 @@
         <v>2.96</v>
       </c>
       <c r="AU89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV89">
         <v>6</v>
       </c>
       <c r="AW89">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX89">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY89">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ89">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA89">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -19255,22 +19255,22 @@
         <v>2.96</v>
       </c>
       <c r="AU89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV89">
         <v>6</v>
       </c>
       <c r="AW89">
+        <v>5</v>
+      </c>
+      <c r="AX89">
         <v>7</v>
       </c>
-      <c r="AX89">
-        <v>9</v>
-      </c>
       <c r="AY89">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ89">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA89">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="204">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -470,6 +470,9 @@
   </si>
   <si>
     <t>['56']</t>
+  </si>
+  <si>
+    <t>['10']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -984,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP89"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1318,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ2">
         <v>0.57</v>
@@ -1446,7 +1449,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1527,7 +1530,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ3">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1652,7 +1655,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1858,7 +1861,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -3094,7 +3097,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3506,7 +3509,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3712,7 +3715,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3918,7 +3921,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -3999,7 +4002,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4124,7 +4127,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4330,7 +4333,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4408,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ17">
         <v>0.71</v>
@@ -4536,7 +4539,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4948,7 +4951,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5154,7 +5157,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5566,7 +5569,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5978,7 +5981,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6184,7 +6187,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6265,7 +6268,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ26">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -7008,7 +7011,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7086,7 +7089,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ30">
         <v>0.38</v>
@@ -7214,7 +7217,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7626,7 +7629,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7832,7 +7835,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8244,7 +8247,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8737,7 +8740,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ38">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.74</v>
@@ -9068,7 +9071,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9274,7 +9277,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9480,7 +9483,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9558,7 +9561,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ42">
         <v>1.43</v>
@@ -9686,7 +9689,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9892,7 +9895,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10510,7 +10513,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10716,7 +10719,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11128,7 +11131,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11334,7 +11337,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11540,7 +11543,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11746,7 +11749,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11952,7 +11955,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12030,7 +12033,7 @@
         <v>0.6</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ54">
         <v>1.13</v>
@@ -12158,7 +12161,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12445,7 +12448,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ56">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.86</v>
@@ -12982,7 +12985,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13266,7 +13269,7 @@
         <v>1.25</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ60">
         <v>1.29</v>
@@ -13394,7 +13397,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13600,7 +13603,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -14012,7 +14015,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14424,7 +14427,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14630,7 +14633,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14917,7 +14920,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.56</v>
@@ -15042,7 +15045,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15248,7 +15251,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15454,7 +15457,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15660,7 +15663,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -15944,7 +15947,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16072,7 +16075,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16278,7 +16281,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16690,7 +16693,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16896,7 +16899,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17102,7 +17105,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17308,7 +17311,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17514,7 +17517,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18132,7 +18135,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -19162,7 +19165,7 @@
         <v>151</v>
       </c>
       <c r="P89" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q89">
         <v>3</v>
@@ -19319,6 +19322,212 @@
       </c>
       <c r="BP89">
         <v>1.77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7796955</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45857.45833333334</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>70</v>
+      </c>
+      <c r="H90" t="s">
+        <v>76</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>152</v>
+      </c>
+      <c r="P90" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q90">
+        <v>1.78</v>
+      </c>
+      <c r="R90">
+        <v>2.7</v>
+      </c>
+      <c r="S90">
+        <v>5.03</v>
+      </c>
+      <c r="T90">
+        <v>1.22</v>
+      </c>
+      <c r="U90">
+        <v>3.6</v>
+      </c>
+      <c r="V90">
+        <v>2.1</v>
+      </c>
+      <c r="W90">
+        <v>1.65</v>
+      </c>
+      <c r="X90">
+        <v>4.6</v>
+      </c>
+      <c r="Y90">
+        <v>1.17</v>
+      </c>
+      <c r="Z90">
+        <v>1.35</v>
+      </c>
+      <c r="AA90">
+        <v>4.9</v>
+      </c>
+      <c r="AB90">
+        <v>6.5</v>
+      </c>
+      <c r="AC90">
+        <v>1.01</v>
+      </c>
+      <c r="AD90">
+        <v>16</v>
+      </c>
+      <c r="AE90">
+        <v>1.13</v>
+      </c>
+      <c r="AF90">
+        <v>5</v>
+      </c>
+      <c r="AG90">
+        <v>1.42</v>
+      </c>
+      <c r="AH90">
+        <v>2.65</v>
+      </c>
+      <c r="AI90">
+        <v>1.73</v>
+      </c>
+      <c r="AJ90">
+        <v>2</v>
+      </c>
+      <c r="AK90">
+        <v>1.17</v>
+      </c>
+      <c r="AL90">
+        <v>1.17</v>
+      </c>
+      <c r="AM90">
+        <v>2.83</v>
+      </c>
+      <c r="AN90">
+        <v>2</v>
+      </c>
+      <c r="AO90">
+        <v>1.17</v>
+      </c>
+      <c r="AP90">
+        <v>2.13</v>
+      </c>
+      <c r="AQ90">
+        <v>1</v>
+      </c>
+      <c r="AR90">
+        <v>2.09</v>
+      </c>
+      <c r="AS90">
+        <v>1.16</v>
+      </c>
+      <c r="AT90">
+        <v>3.25</v>
+      </c>
+      <c r="AU90">
+        <v>7</v>
+      </c>
+      <c r="AV90">
+        <v>3</v>
+      </c>
+      <c r="AW90">
+        <v>12</v>
+      </c>
+      <c r="AX90">
+        <v>5</v>
+      </c>
+      <c r="AY90">
+        <v>19</v>
+      </c>
+      <c r="AZ90">
+        <v>8</v>
+      </c>
+      <c r="BA90">
+        <v>5</v>
+      </c>
+      <c r="BB90">
+        <v>2</v>
+      </c>
+      <c r="BC90">
+        <v>7</v>
+      </c>
+      <c r="BD90">
+        <v>1.12</v>
+      </c>
+      <c r="BE90">
+        <v>12.5</v>
+      </c>
+      <c r="BF90">
+        <v>7.9</v>
+      </c>
+      <c r="BG90">
+        <v>1.13</v>
+      </c>
+      <c r="BH90">
+        <v>5</v>
+      </c>
+      <c r="BI90">
+        <v>1.19</v>
+      </c>
+      <c r="BJ90">
+        <v>3.6</v>
+      </c>
+      <c r="BK90">
+        <v>1.42</v>
+      </c>
+      <c r="BL90">
+        <v>2.62</v>
+      </c>
+      <c r="BM90">
+        <v>1.67</v>
+      </c>
+      <c r="BN90">
+        <v>2.1</v>
+      </c>
+      <c r="BO90">
+        <v>2.05</v>
+      </c>
+      <c r="BP90">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,9 @@
     <t>['10']</t>
   </si>
   <si>
+    <t>['66']</t>
+  </si>
+  <si>
     <t>['46']</t>
   </si>
   <si>
@@ -626,6 +629,9 @@
   </si>
   <si>
     <t>['69', '65']</t>
+  </si>
+  <si>
+    <t>['40', '89']</t>
   </si>
 </sst>
 </file>
@@ -987,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1449,7 +1455,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1655,7 +1661,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1861,7 +1867,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -2145,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2969,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ10">
         <v>0.88</v>
@@ -3097,7 +3103,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3509,7 +3515,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3590,7 +3596,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ13">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3715,7 +3721,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3921,7 +3927,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4127,7 +4133,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4333,7 +4339,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4539,7 +4545,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4951,7 +4957,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5157,7 +5163,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5569,7 +5575,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5981,7 +5987,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6187,7 +6193,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6680,7 +6686,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ28">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -7011,7 +7017,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7217,7 +7223,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7295,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7629,7 +7635,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7835,7 +7841,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8247,7 +8253,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -8531,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ37">
         <v>0.38</v>
@@ -9071,7 +9077,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9277,7 +9283,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9483,7 +9489,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9564,7 +9570,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ42">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR42">
         <v>2.48</v>
@@ -9689,7 +9695,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9895,7 +9901,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10513,7 +10519,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10719,7 +10725,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -10797,7 +10803,7 @@
         <v>0.75</v>
       </c>
       <c r="AP48">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ48">
         <v>1.13</v>
@@ -11131,7 +11137,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11337,7 +11343,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11418,7 +11424,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ51">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR51">
         <v>1.5</v>
@@ -11543,7 +11549,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11749,7 +11755,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11955,7 +11961,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12161,7 +12167,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12985,7 +12991,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13397,7 +13403,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13603,7 +13609,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -13684,7 +13690,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -14015,7 +14021,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14427,7 +14433,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14633,7 +14639,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -14711,7 +14717,7 @@
         <v>0.6</v>
       </c>
       <c r="AP67">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ67">
         <v>0.38</v>
@@ -15045,7 +15051,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15251,7 +15257,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15457,7 +15463,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15663,7 +15669,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16075,7 +16081,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16156,7 +16162,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ74">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16281,7 +16287,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16693,7 +16699,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16899,7 +16905,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -16977,7 +16983,7 @@
         <v>0.67</v>
       </c>
       <c r="AP78">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AQ78">
         <v>0.57</v>
@@ -17105,7 +17111,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17311,7 +17317,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17517,7 +17523,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -17598,7 +17604,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR81">
         <v>1.09</v>
@@ -18135,7 +18141,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -19165,7 +19171,7 @@
         <v>151</v>
       </c>
       <c r="P89" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q89">
         <v>3</v>
@@ -19527,6 +19533,212 @@
         <v>2.05</v>
       </c>
       <c r="BP90">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7796891</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45858.67708333334</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>74</v>
+      </c>
+      <c r="H91" t="s">
+        <v>71</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>3</v>
+      </c>
+      <c r="O91" t="s">
+        <v>153</v>
+      </c>
+      <c r="P91" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q91">
+        <v>2.5</v>
+      </c>
+      <c r="R91">
+        <v>2.15</v>
+      </c>
+      <c r="S91">
+        <v>3.75</v>
+      </c>
+      <c r="T91">
+        <v>1.29</v>
+      </c>
+      <c r="U91">
+        <v>3.3</v>
+      </c>
+      <c r="V91">
+        <v>2.25</v>
+      </c>
+      <c r="W91">
+        <v>1.57</v>
+      </c>
+      <c r="X91">
+        <v>5</v>
+      </c>
+      <c r="Y91">
+        <v>1.15</v>
+      </c>
+      <c r="Z91">
+        <v>2.21</v>
+      </c>
+      <c r="AA91">
+        <v>3.4</v>
+      </c>
+      <c r="AB91">
+        <v>3.34</v>
+      </c>
+      <c r="AC91">
+        <v>1</v>
+      </c>
+      <c r="AD91">
+        <v>12</v>
+      </c>
+      <c r="AE91">
+        <v>1.12</v>
+      </c>
+      <c r="AF91">
+        <v>4.5</v>
+      </c>
+      <c r="AG91">
+        <v>1.4</v>
+      </c>
+      <c r="AH91">
+        <v>2.25</v>
+      </c>
+      <c r="AI91">
+        <v>1.5</v>
+      </c>
+      <c r="AJ91">
+        <v>2.52</v>
+      </c>
+      <c r="AK91">
+        <v>1.3</v>
+      </c>
+      <c r="AL91">
+        <v>1.3</v>
+      </c>
+      <c r="AM91">
+        <v>1.73</v>
+      </c>
+      <c r="AN91">
+        <v>3</v>
+      </c>
+      <c r="AO91">
+        <v>1.43</v>
+      </c>
+      <c r="AP91">
+        <v>2.63</v>
+      </c>
+      <c r="AQ91">
+        <v>1.63</v>
+      </c>
+      <c r="AR91">
+        <v>1.59</v>
+      </c>
+      <c r="AS91">
+        <v>1.48</v>
+      </c>
+      <c r="AT91">
+        <v>3.07</v>
+      </c>
+      <c r="AU91">
+        <v>4</v>
+      </c>
+      <c r="AV91">
+        <v>8</v>
+      </c>
+      <c r="AW91">
+        <v>5</v>
+      </c>
+      <c r="AX91">
+        <v>6</v>
+      </c>
+      <c r="AY91">
+        <v>9</v>
+      </c>
+      <c r="AZ91">
+        <v>14</v>
+      </c>
+      <c r="BA91">
+        <v>3</v>
+      </c>
+      <c r="BB91">
+        <v>3</v>
+      </c>
+      <c r="BC91">
+        <v>6</v>
+      </c>
+      <c r="BD91">
+        <v>1.75</v>
+      </c>
+      <c r="BE91">
+        <v>7.1</v>
+      </c>
+      <c r="BF91">
+        <v>2.65</v>
+      </c>
+      <c r="BG91">
+        <v>1.13</v>
+      </c>
+      <c r="BH91">
+        <v>5</v>
+      </c>
+      <c r="BI91">
+        <v>1.18</v>
+      </c>
+      <c r="BJ91">
+        <v>3.84</v>
+      </c>
+      <c r="BK91">
+        <v>1.36</v>
+      </c>
+      <c r="BL91">
+        <v>2.62</v>
+      </c>
+      <c r="BM91">
+        <v>1.67</v>
+      </c>
+      <c r="BN91">
+        <v>2.1</v>
+      </c>
+      <c r="BO91">
+        <v>2.05</v>
+      </c>
+      <c r="BP91">
         <v>1.7</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -19676,22 +19676,22 @@
         <v>3.07</v>
       </c>
       <c r="AU91">
+        <v>2</v>
+      </c>
+      <c r="AV91">
+        <v>10</v>
+      </c>
+      <c r="AW91">
         <v>4</v>
       </c>
-      <c r="AV91">
-        <v>8</v>
-      </c>
-      <c r="AW91">
-        <v>5</v>
-      </c>
       <c r="AX91">
+        <v>2</v>
+      </c>
+      <c r="AY91">
         <v>6</v>
       </c>
-      <c r="AY91">
-        <v>9</v>
-      </c>
       <c r="AZ91">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA91">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Iceland Úrvalsdeild_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="205">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -473,9 +473,6 @@
   </si>
   <si>
     <t>['10']</t>
-  </si>
-  <si>
-    <t>['66']</t>
   </si>
   <si>
     <t>['46']</t>
@@ -1455,7 +1452,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>1.73</v>
@@ -1661,7 +1658,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1867,7 +1864,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q5">
         <v>2.83</v>
@@ -3103,7 +3100,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -3515,7 +3512,7 @@
         <v>92</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3721,7 +3718,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>1.88</v>
@@ -3927,7 +3924,7 @@
         <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4133,7 +4130,7 @@
         <v>94</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4339,7 +4336,7 @@
         <v>95</v>
       </c>
       <c r="P17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -4545,7 +4542,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q18">
         <v>2.84</v>
@@ -4957,7 +4954,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -5163,7 +5160,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>2.74</v>
@@ -5575,7 +5572,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
@@ -5987,7 +5984,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6193,7 +6190,7 @@
         <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -7017,7 +7014,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7223,7 +7220,7 @@
         <v>107</v>
       </c>
       <c r="P31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q31">
         <v>1.79</v>
@@ -7635,7 +7632,7 @@
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -7841,7 +7838,7 @@
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q34">
         <v>1.95</v>
@@ -8253,7 +8250,7 @@
         <v>85</v>
       </c>
       <c r="P36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q36">
         <v>4.7</v>
@@ -9077,7 +9074,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9283,7 +9280,7 @@
         <v>115</v>
       </c>
       <c r="P41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9489,7 +9486,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9695,7 +9692,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -9901,7 +9898,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>2.15</v>
@@ -10519,7 +10516,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>3.15</v>
@@ -10725,7 +10722,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>1.5</v>
@@ -11137,7 +11134,7 @@
         <v>85</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q50">
         <v>4.78</v>
@@ -11343,7 +11340,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q51">
         <v>3.8</v>
@@ -11549,7 +11546,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11755,7 +11752,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q53">
         <v>2.7</v>
@@ -11961,7 +11958,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q54">
         <v>1.8</v>
@@ -12167,7 +12164,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -12991,7 +12988,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q59">
         <v>2.61</v>
@@ -13403,7 +13400,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -13609,7 +13606,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q62">
         <v>3.55</v>
@@ -14021,7 +14018,7 @@
         <v>85</v>
       </c>
       <c r="P64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -14433,7 +14430,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q66">
         <v>2.68</v>
@@ -14639,7 +14636,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -15051,7 +15048,7 @@
         <v>85</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15257,7 +15254,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>3.05</v>
@@ -15463,7 +15460,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q71">
         <v>2.61</v>
@@ -15669,7 +15666,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>2.36</v>
@@ -16081,7 +16078,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q74">
         <v>3.15</v>
@@ -16287,7 +16284,7 @@
         <v>142</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>2.7</v>
@@ -16699,7 +16696,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16905,7 +16902,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q78">
         <v>1.71</v>
@@ -17111,7 +17108,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17317,7 +17314,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q80">
         <v>3.9</v>
@@ -17523,7 +17520,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>4.45</v>
@@ -18141,7 +18138,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q84">
         <v>2.23</v>
@@ -19171,7 +19168,7 @@
         <v>151</v>
       </c>
       <c r="P89" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q89">
         <v>3</v>
@@ -19553,7 +19550,7 @@
         <v>45858.67708333334</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
         <v>74</v>
@@ -19580,10 +19577,10 @@
         <v>3</v>
       </c>
       <c r="O91" t="s">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
